--- a/natural-language-processing/exports/mia07_t3_tra_resultados_trans.xlsx
+++ b/natural-language-processing/exports/mia07_t3_tra_resultados_trans.xlsx
@@ -26,12 +26,17 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007FFFD4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1099,46 +1105,46 @@
           <t>q0</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="1" t="n">
         <v>0.1965317919075145</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="1" t="n">
         <v>0.01734104046242774</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.2774566473988439</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.05780346820809248</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.04046242774566474</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.0115606936416185</v>
       </c>
       <c r="P2" t="n">
@@ -1150,10 +1156,10 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.02312138728323699</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="U2" t="n">
@@ -1165,10 +1171,10 @@
       <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2" s="1" t="n">
         <v>0.01734104046242774</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="Z2" t="n">
@@ -1177,13 +1183,13 @@
       <c r="AA2" t="n">
         <v>0</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.138728323699422</v>
       </c>
       <c r="AE2" t="n">
@@ -1213,25 +1219,25 @@
       <c r="AM2" t="n">
         <v>0</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AP2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AR2" s="1" t="n">
         <v>0.01734104046242774</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AT2" s="1" t="n">
         <v>0.02890173410404624</v>
       </c>
       <c r="AU2" t="n">
@@ -1243,10 +1249,10 @@
       <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AX2" s="1" t="n">
         <v>0.0115606936416185</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AY2" s="1" t="n">
         <v>0.02312138728323699</v>
       </c>
       <c r="AZ2" t="n">
@@ -1255,7 +1261,7 @@
       <c r="BA2" t="n">
         <v>0</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" s="1" t="n">
         <v>0.0115606936416185</v>
       </c>
       <c r="BC2" t="n">
@@ -1285,7 +1291,7 @@
       <c r="BK2" t="n">
         <v>0</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BL2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="BM2" t="n">
@@ -1360,13 +1366,13 @@
       <c r="CJ2" t="n">
         <v>0</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CK2" s="1" t="n">
         <v>0.0115606936416185</v>
       </c>
       <c r="CL2" t="n">
         <v>0</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CM2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="CN2" t="n">
@@ -1411,7 +1417,7 @@
       <c r="DA2" t="n">
         <v>0</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DB2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="DC2" t="n">
@@ -1450,7 +1456,7 @@
       <c r="DN2" t="n">
         <v>0</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DO2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="DP2" t="n">
@@ -1474,7 +1480,7 @@
       <c r="DV2" t="n">
         <v>0</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="DW2" s="1" t="n">
         <v>0.005780346820809248</v>
       </c>
       <c r="DX2" t="n">
@@ -1498,7 +1504,7 @@
       <c r="ED2" t="n">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
+      <c r="EE2" s="1" t="n">
         <v>0.0115606936416185</v>
       </c>
       <c r="EF2" t="n">
@@ -1514,7 +1520,7 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1" t="n">
         <v>0.021875</v>
       </c>
       <c r="D3" t="n">
@@ -1523,52 +1529,52 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.078125</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.003125</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="1" t="n">
         <v>0.009375</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.003125</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.14375</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.003125</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.003125</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.00625</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.01875</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="1" t="n">
         <v>0.00625</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="1" t="n">
         <v>0.00625</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="1" t="n">
         <v>0.08125</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="V3" t="n">
@@ -1577,10 +1583,10 @@
       <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3" s="1" t="n">
         <v>0.015625</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" s="1" t="n">
         <v>0.040625</v>
       </c>
       <c r="Z3" t="n">
@@ -1595,7 +1601,7 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.009375</v>
       </c>
       <c r="AE3" t="n">
@@ -1607,13 +1613,13 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH3" s="1" t="n">
         <v>0.003125</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI3" s="1" t="n">
         <v>0.040625</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>0.159375</v>
       </c>
       <c r="AK3" t="n">
@@ -1637,28 +1643,28 @@
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AT3" s="1" t="n">
         <v>0.059375</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AU3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AW3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AY3" s="1" t="n">
         <v>0.0125</v>
       </c>
       <c r="AZ3" t="n">
@@ -1673,16 +1679,16 @@
       <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BD3" s="1" t="n">
         <v>0.00625</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BF3" s="1" t="n">
         <v>0.00625</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BG3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="BH3" t="n">
@@ -1691,7 +1697,7 @@
       <c r="BI3" t="n">
         <v>0</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BJ3" s="1" t="n">
         <v>0.00625</v>
       </c>
       <c r="BK3" t="n">
@@ -1700,7 +1706,7 @@
       <c r="BL3" t="n">
         <v>0</v>
       </c>
-      <c r="BM3" t="n">
+      <c r="BM3" s="1" t="n">
         <v>0.046875</v>
       </c>
       <c r="BN3" t="n">
@@ -1709,10 +1715,10 @@
       <c r="BO3" t="n">
         <v>0</v>
       </c>
-      <c r="BP3" t="n">
+      <c r="BP3" s="1" t="n">
         <v>0.053125</v>
       </c>
-      <c r="BQ3" t="n">
+      <c r="BQ3" s="1" t="n">
         <v>0.0375</v>
       </c>
       <c r="BR3" t="n">
@@ -1721,13 +1727,13 @@
       <c r="BS3" t="n">
         <v>0</v>
       </c>
-      <c r="BT3" t="n">
+      <c r="BT3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="BV3" s="1" t="n">
         <v>0.0375</v>
       </c>
       <c r="BW3" t="n">
@@ -1751,10 +1757,10 @@
       <c r="CC3" t="n">
         <v>0</v>
       </c>
-      <c r="CD3" t="n">
+      <c r="CD3" s="1" t="n">
         <v>0.009375</v>
       </c>
-      <c r="CE3" t="n">
+      <c r="CE3" s="1" t="n">
         <v>0.00625</v>
       </c>
       <c r="CF3" t="n">
@@ -1826,7 +1832,7 @@
       <c r="DB3" t="n">
         <v>0</v>
       </c>
-      <c r="DC3" t="n">
+      <c r="DC3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="DD3" t="n">
@@ -1835,7 +1841,7 @@
       <c r="DE3" t="n">
         <v>0</v>
       </c>
-      <c r="DF3" t="n">
+      <c r="DF3" s="1" t="n">
         <v>0.00625</v>
       </c>
       <c r="DG3" t="n">
@@ -1850,22 +1856,22 @@
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
-      <c r="DK3" t="n">
+      <c r="DK3" s="1" t="n">
         <v>0.009375</v>
       </c>
-      <c r="DL3" t="n">
+      <c r="DL3" s="1" t="n">
         <v>0.015625</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
-      <c r="DN3" t="n">
+      <c r="DN3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
-      <c r="DP3" t="n">
+      <c r="DP3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="DQ3" t="n">
@@ -1883,7 +1889,7 @@
       <c r="DU3" t="n">
         <v>0</v>
       </c>
-      <c r="DV3" t="n">
+      <c r="DV3" s="1" t="n">
         <v>0.003125</v>
       </c>
       <c r="DW3" t="n">
@@ -1929,16 +1935,16 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="1" t="n">
         <v>0.1612903225806452</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.06451612903225806</v>
       </c>
       <c r="H4" t="n">
@@ -1947,7 +1953,7 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.1290322580645161</v>
       </c>
       <c r="K4" t="n">
@@ -1956,7 +1962,7 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.1290322580645161</v>
       </c>
       <c r="N4" t="n">
@@ -1965,13 +1971,13 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="1" t="n">
         <v>0.09677419354838709</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="S4" t="n">
@@ -1989,7 +1995,7 @@
       <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="Y4" t="n">
@@ -2007,7 +2013,7 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="AE4" t="n">
@@ -2016,7 +2022,7 @@
       <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG4" s="1" t="n">
         <v>0.09677419354838709</v>
       </c>
       <c r="AH4" t="n">
@@ -2043,7 +2049,7 @@
       <c r="AO4" t="n">
         <v>0</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP4" s="1" t="n">
         <v>0.09677419354838709</v>
       </c>
       <c r="AQ4" t="n">
@@ -2097,7 +2103,7 @@
       <c r="BG4" t="n">
         <v>0</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BH4" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="BI4" t="n">
@@ -2112,7 +2118,7 @@
       <c r="BL4" t="n">
         <v>0</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BM4" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="BN4" t="n">
@@ -2344,10 +2350,10 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="1" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.06521739130434782</v>
       </c>
       <c r="G5" t="n">
@@ -2377,19 +2383,19 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="1" t="n">
         <v>0.06521739130434782</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.06521739130434782</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="1" t="n">
         <v>0.02173913043478261</v>
       </c>
       <c r="U5" t="n">
@@ -2437,7 +2443,7 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>0.02173913043478261</v>
       </c>
       <c r="AK5" t="n">
@@ -2524,7 +2530,7 @@
       <c r="BL5" t="n">
         <v>0</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BM5" s="1" t="n">
         <v>0.02173913043478261</v>
       </c>
       <c r="BN5" t="n">
@@ -2747,10 +2753,10 @@
           <t>NCFS000</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="1" t="n">
         <v>0.02583025830258303</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="1" t="n">
         <v>0.01107011070110701</v>
       </c>
       <c r="D6" t="n">
@@ -2759,49 +2765,49 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.3616236162361623</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.0959409594095941</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.02214022140221402</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.01476014760147601</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="1" t="n">
         <v>0.06642066420664207</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="1" t="n">
         <v>0.007380073800738007</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.06273062730627306</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" s="1" t="n">
         <v>0.04059040590405904</v>
       </c>
       <c r="U6" t="n">
@@ -2813,10 +2819,10 @@
       <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6" s="1" t="n">
         <v>0.01107011070110701</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6" s="1" t="n">
         <v>0.01476014760147601</v>
       </c>
       <c r="Z6" t="n">
@@ -2831,7 +2837,7 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.01845018450184502</v>
       </c>
       <c r="AE6" t="n">
@@ -2846,10 +2852,10 @@
       <c r="AH6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AI6" s="1" t="n">
         <v>0.007380073800738007</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>0.06642066420664207</v>
       </c>
       <c r="AK6" t="n">
@@ -2867,25 +2873,25 @@
       <c r="AO6" t="n">
         <v>0</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AP6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AR6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AT6" s="1" t="n">
         <v>0.03321033210332103</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="AW6" t="n">
@@ -2894,7 +2900,7 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AY6" s="1" t="n">
         <v>0.02214022140221402</v>
       </c>
       <c r="AZ6" t="n">
@@ -2903,25 +2909,25 @@
       <c r="BA6" t="n">
         <v>0</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BD6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BF6" s="1" t="n">
         <v>0.04059040590405904</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BH6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="BI6" t="n">
@@ -2936,7 +2942,7 @@
       <c r="BL6" t="n">
         <v>0</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="BM6" s="1" t="n">
         <v>0.01107011070110701</v>
       </c>
       <c r="BN6" t="n">
@@ -2945,10 +2951,10 @@
       <c r="BO6" t="n">
         <v>0</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BP6" s="1" t="n">
         <v>0.007380073800738007</v>
       </c>
-      <c r="BQ6" t="n">
+      <c r="BQ6" s="1" t="n">
         <v>0.007380073800738007</v>
       </c>
       <c r="BR6" t="n">
@@ -2963,7 +2969,7 @@
       <c r="BU6" t="n">
         <v>0</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="BV6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="BW6" t="n">
@@ -2975,7 +2981,7 @@
       <c r="BY6" t="n">
         <v>0</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="BZ6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="CA6" t="n">
@@ -3077,19 +3083,19 @@
       <c r="DG6" t="n">
         <v>0</v>
       </c>
-      <c r="DH6" t="n">
+      <c r="DH6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
-      <c r="DJ6" t="n">
+      <c r="DJ6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
-      <c r="DL6" t="n">
+      <c r="DL6" s="1" t="n">
         <v>0.003690036900369004</v>
       </c>
       <c r="DM6" t="n">
@@ -3159,28 +3165,28 @@
           <t>SPS00</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="1" t="n">
         <v>0.1493411420204978</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="1" t="n">
         <v>0.01903367496339678</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="1" t="n">
         <v>0.05856515373352855</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.1493411420204978</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="1" t="n">
         <v>0.04538799414348463</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="J7" t="n">
@@ -3195,13 +3201,13 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.1361639824304539</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="Q7" t="n">
@@ -3210,7 +3216,7 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.03806734992679356</v>
       </c>
       <c r="T7" t="n">
@@ -3219,40 +3225,40 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.01171303074670571</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.01317715959004392</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7" s="1" t="n">
         <v>0.02196193265007321</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.007320644216691069</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.005856515373352855</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.0322108345534407</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.008784773060029283</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AF7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AG7" s="1" t="n">
         <v>0.06442166910688141</v>
       </c>
       <c r="AH7" t="n">
@@ -3273,19 +3279,19 @@
       <c r="AM7" t="n">
         <v>0</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO7" s="1" t="n">
         <v>0.01171303074670571</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP7" s="1" t="n">
         <v>0.03953147877013177</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR7" s="1" t="n">
         <v>0.0424597364568082</v>
       </c>
       <c r="AS7" t="n">
@@ -3297,13 +3303,13 @@
       <c r="AU7" t="n">
         <v>0</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AV7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AX7" s="1" t="n">
         <v>0.01317715959004392</v>
       </c>
       <c r="AY7" t="n">
@@ -3315,40 +3321,40 @@
       <c r="BA7" t="n">
         <v>0</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" s="1" t="n">
         <v>0.03806734992679356</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BC7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BE7" s="1" t="n">
         <v>0.004392386530014641</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BF7" s="1" t="n">
         <v>0.0102489019033675</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BH7" s="1" t="n">
         <v>0.01171303074670571</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BI7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BJ7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BK7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BL7" s="1" t="n">
         <v>0.0102489019033675</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BM7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
       <c r="BN7" t="n">
@@ -3369,7 +3375,7 @@
       <c r="BS7" t="n">
         <v>0</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="BT7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="BU7" t="n">
@@ -3384,7 +3390,7 @@
       <c r="BX7" t="n">
         <v>0</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="BY7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="BZ7" t="n">
@@ -3396,7 +3402,7 @@
       <c r="CB7" t="n">
         <v>0</v>
       </c>
-      <c r="CC7" t="n">
+      <c r="CC7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="CD7" t="n">
@@ -3420,13 +3426,13 @@
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CK7" s="1" t="n">
         <v>0.004392386530014641</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CL7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
-      <c r="CM7" t="n">
+      <c r="CM7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
       <c r="CN7" t="n">
@@ -3435,13 +3441,13 @@
       <c r="CO7" t="n">
         <v>0</v>
       </c>
-      <c r="CP7" t="n">
+      <c r="CP7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
-      <c r="CQ7" t="n">
+      <c r="CQ7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
-      <c r="CR7" t="n">
+      <c r="CR7" s="1" t="n">
         <v>0.002928257686676428</v>
       </c>
       <c r="CS7" t="n">
@@ -3480,7 +3486,7 @@
       <c r="DD7" t="n">
         <v>0</v>
       </c>
-      <c r="DE7" t="n">
+      <c r="DE7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="DF7" t="n">
@@ -3492,7 +3498,7 @@
       <c r="DH7" t="n">
         <v>0</v>
       </c>
-      <c r="DI7" t="n">
+      <c r="DI7" s="1" t="n">
         <v>0.004392386530014641</v>
       </c>
       <c r="DJ7" t="n">
@@ -3516,7 +3522,7 @@
       <c r="DP7" t="n">
         <v>0</v>
       </c>
-      <c r="DQ7" t="n">
+      <c r="DQ7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="DR7" t="n">
@@ -3537,7 +3543,7 @@
       <c r="DW7" t="n">
         <v>0</v>
       </c>
-      <c r="DX7" t="n">
+      <c r="DX7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="DY7" t="n">
@@ -3549,13 +3555,13 @@
       <c r="EA7" t="n">
         <v>0</v>
       </c>
-      <c r="EB7" t="n">
+      <c r="EB7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="EC7" t="n">
         <v>0</v>
       </c>
-      <c r="ED7" t="n">
+      <c r="ED7" s="1" t="n">
         <v>0.001464128843338214</v>
       </c>
       <c r="EE7" t="n">
@@ -3571,7 +3577,7 @@
           <t>DA0MS0</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="1" t="n">
         <v>0.01910828025477707</v>
       </c>
       <c r="C8" t="n">
@@ -3580,19 +3586,19 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="1" t="n">
         <v>0.01910828025477707</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.01273885350318471</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="1" t="n">
         <v>0.6942675159235668</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.01910828025477707</v>
       </c>
       <c r="J8" t="n">
@@ -3613,7 +3619,7 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="1" t="n">
         <v>0.01910828025477707</v>
       </c>
       <c r="Q8" t="n">
@@ -3622,7 +3628,7 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="1" t="n">
         <v>0.006369426751592357</v>
       </c>
       <c r="T8" t="n">
@@ -3664,7 +3670,7 @@
       <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG8" s="1" t="n">
         <v>0.04458598726114649</v>
       </c>
       <c r="AH8" t="n">
@@ -3691,7 +3697,7 @@
       <c r="AO8" t="n">
         <v>0</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AP8" s="1" t="n">
         <v>0.01273885350318471</v>
       </c>
       <c r="AQ8" t="n">
@@ -3721,10 +3727,10 @@
       <c r="AY8" t="n">
         <v>0</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="AZ8" s="1" t="n">
         <v>0.05732484076433121</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BA8" s="1" t="n">
         <v>0.04458598726114649</v>
       </c>
       <c r="BB8" t="n">
@@ -3739,7 +3745,7 @@
       <c r="BE8" t="n">
         <v>0</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BF8" s="1" t="n">
         <v>0.01910828025477707</v>
       </c>
       <c r="BG8" t="n">
@@ -3754,7 +3760,7 @@
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BK8" s="1" t="n">
         <v>0.01273885350318471</v>
       </c>
       <c r="BL8" t="n">
@@ -3796,7 +3802,7 @@
       <c r="BX8" t="n">
         <v>0</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="BY8" s="1" t="n">
         <v>0.006369426751592357</v>
       </c>
       <c r="BZ8" t="n">
@@ -3805,7 +3811,7 @@
       <c r="CA8" t="n">
         <v>0</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CB8" s="1" t="n">
         <v>0.01273885350318471</v>
       </c>
       <c r="CC8" t="n">
@@ -3983,10 +3989,10 @@
           <t>NCMS000</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="1" t="n">
         <v>0.0402930402930403</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>0.007326007326007326</v>
       </c>
       <c r="D9" t="n">
@@ -3995,40 +4001,40 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.3223443223443224</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="1" t="n">
         <v>0.007326007326007326</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="1" t="n">
         <v>0.01098901098901099</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="1" t="n">
         <v>0.0402930402930403</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="1" t="n">
         <v>0.01831501831501832</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.07326007326007326</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.007326007326007326</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="1" t="n">
         <v>0.01098901098901099</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="1" t="n">
         <v>0.05494505494505494</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="R9" t="n">
@@ -4037,7 +4043,7 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="1" t="n">
         <v>0.08058608058608059</v>
       </c>
       <c r="U9" t="n">
@@ -4049,7 +4055,7 @@
       <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X9" s="1" t="n">
         <v>0.01098901098901099</v>
       </c>
       <c r="Y9" t="n">
@@ -4067,7 +4073,7 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD9" s="1" t="n">
         <v>0.01098901098901099</v>
       </c>
       <c r="AE9" t="n">
@@ -4085,7 +4091,7 @@
       <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>0.1135531135531136</v>
       </c>
       <c r="AK9" t="n">
@@ -4106,7 +4112,7 @@
       <c r="AP9" t="n">
         <v>0</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="AR9" t="n">
@@ -4115,13 +4121,13 @@
       <c r="AS9" t="n">
         <v>0</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT9" s="1" t="n">
         <v>0.02197802197802198</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AV9" s="1" t="n">
         <v>0.007326007326007326</v>
       </c>
       <c r="AW9" t="n">
@@ -4130,7 +4136,7 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AY9" s="1" t="n">
         <v>0.01098901098901099</v>
       </c>
       <c r="AZ9" t="n">
@@ -4148,10 +4154,10 @@
       <c r="BD9" t="n">
         <v>0</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BE9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BF9" s="1" t="n">
         <v>0.05128205128205128</v>
       </c>
       <c r="BG9" t="n">
@@ -4172,7 +4178,7 @@
       <c r="BL9" t="n">
         <v>0</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BM9" s="1" t="n">
         <v>0.01831501831501832</v>
       </c>
       <c r="BN9" t="n">
@@ -4181,10 +4187,10 @@
       <c r="BO9" t="n">
         <v>0</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BP9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BQ9" s="1" t="n">
         <v>0.03663003663003663</v>
       </c>
       <c r="BR9" t="n">
@@ -4241,19 +4247,19 @@
       <c r="CI9" t="n">
         <v>0</v>
       </c>
-      <c r="CJ9" t="n">
+      <c r="CJ9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CL9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
-      <c r="CN9" t="n">
+      <c r="CN9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="CO9" t="n">
@@ -4292,7 +4298,7 @@
       <c r="CZ9" t="n">
         <v>0</v>
       </c>
-      <c r="DA9" t="n">
+      <c r="DA9" s="1" t="n">
         <v>0.003663003663003663</v>
       </c>
       <c r="DB9" t="n">
@@ -4322,7 +4328,7 @@
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
-      <c r="DK9" t="n">
+      <c r="DK9" s="1" t="n">
         <v>0.01098901098901099</v>
       </c>
       <c r="DL9" t="n">
@@ -4395,7 +4401,7 @@
           <t>AQ0MS0</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="1" t="n">
         <v>0.04878048780487805</v>
       </c>
       <c r="C10" t="n">
@@ -4407,22 +4413,22 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="1" t="n">
         <v>0.3414634146341464</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="1" t="n">
         <v>0.2195121951219512</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="L10" t="n">
@@ -4434,7 +4440,7 @@
       <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="P10" t="n">
@@ -4449,7 +4455,7 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="U10" t="n">
@@ -4461,7 +4467,7 @@
       <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10" s="1" t="n">
         <v>0.0975609756097561</v>
       </c>
       <c r="Y10" t="n">
@@ -4491,13 +4497,13 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>0.07317073170731707</v>
       </c>
       <c r="AK10" t="n">
@@ -4527,7 +4533,7 @@
       <c r="AS10" t="n">
         <v>0</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AT10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="AU10" t="n">
@@ -4563,7 +4569,7 @@
       <c r="BE10" t="n">
         <v>0</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BF10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="BG10" t="n">
@@ -4605,7 +4611,7 @@
       <c r="BS10" t="n">
         <v>0</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="BT10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="BU10" t="n">
@@ -4749,7 +4755,7 @@
       <c r="DO10" t="n">
         <v>0</v>
       </c>
-      <c r="DP10" t="n">
+      <c r="DP10" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="DQ10" t="n">
@@ -4819,22 +4825,22 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="1" t="n">
         <v>0.4210526315789473</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="1" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="1" t="n">
         <v>0.03947368421052631</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="1" t="n">
         <v>0.02631578947368421</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.03947368421052631</v>
       </c>
       <c r="L11" t="n">
@@ -4849,7 +4855,7 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="Q11" t="n">
@@ -4858,10 +4864,10 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="1" t="n">
         <v>0.06578947368421052</v>
       </c>
       <c r="U11" t="n">
@@ -4873,7 +4879,7 @@
       <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X11" s="1" t="n">
         <v>0.05263157894736842</v>
       </c>
       <c r="Y11" t="n">
@@ -4891,7 +4897,7 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD11" s="1" t="n">
         <v>0.07894736842105263</v>
       </c>
       <c r="AE11" t="n">
@@ -4900,7 +4906,7 @@
       <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG11" s="1" t="n">
         <v>0.02631578947368421</v>
       </c>
       <c r="AH11" t="n">
@@ -4909,7 +4915,7 @@
       <c r="AI11" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>0.09210526315789473</v>
       </c>
       <c r="AK11" t="n">
@@ -4942,7 +4948,7 @@
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AU11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="AV11" t="n">
@@ -4975,13 +4981,13 @@
       <c r="BE11" t="n">
         <v>0</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BF11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BH11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="BI11" t="n">
@@ -4993,10 +4999,10 @@
       <c r="BK11" t="n">
         <v>0</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BL11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BM11" s="1" t="n">
         <v>0.02631578947368421</v>
       </c>
       <c r="BN11" t="n">
@@ -5005,7 +5011,7 @@
       <c r="BO11" t="n">
         <v>0</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BP11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="BQ11" t="n">
@@ -5134,7 +5140,7 @@
       <c r="DF11" t="n">
         <v>0</v>
       </c>
-      <c r="DG11" t="n">
+      <c r="DG11" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="DH11" t="n">
@@ -5231,7 +5237,7 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="1" t="n">
         <v>0.005617977528089887</v>
       </c>
       <c r="G12" t="n">
@@ -5246,7 +5252,7 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="1" t="n">
         <v>0.005617977528089887</v>
       </c>
       <c r="L12" t="n">
@@ -5369,7 +5375,7 @@
       <c r="AY12" t="n">
         <v>0</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ12" s="1" t="n">
         <v>0.005617977528089887</v>
       </c>
       <c r="BA12" t="n">
@@ -5408,7 +5414,7 @@
       <c r="BL12" t="n">
         <v>0</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BM12" s="1" t="n">
         <v>0.005617977528089887</v>
       </c>
       <c r="BN12" t="n">
@@ -5417,7 +5423,7 @@
       <c r="BO12" t="n">
         <v>0</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BP12" s="1" t="n">
         <v>0.005617977528089887</v>
       </c>
       <c r="BQ12" t="n">
@@ -5621,7 +5627,7 @@
       <c r="EE12" t="n">
         <v>0</v>
       </c>
-      <c r="EF12" t="n">
+      <c r="EF12" s="1" t="n">
         <v>0.9719101123595506</v>
       </c>
     </row>
@@ -5643,7 +5649,7 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="G13" t="n">
@@ -5655,7 +5661,7 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="1" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="K13" t="n">
@@ -5664,7 +5670,7 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="N13" t="n">
@@ -5751,7 +5757,7 @@
       <c r="AO13" t="n">
         <v>0</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AP13" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="AQ13" t="n">
@@ -6049,13 +6055,13 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="1" t="n">
         <v>0.5806451612903226</v>
       </c>
       <c r="G14" t="n">
@@ -6070,7 +6076,7 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="1" t="n">
         <v>0.1290322580645161</v>
       </c>
       <c r="L14" t="n">
@@ -6097,7 +6103,7 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" s="1" t="n">
         <v>0.1612903225806452</v>
       </c>
       <c r="U14" t="n">
@@ -6232,7 +6238,7 @@
       <c r="BL14" t="n">
         <v>0</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BM14" s="1" t="n">
         <v>0.06451612903225806</v>
       </c>
       <c r="BN14" t="n">
@@ -6455,7 +6461,7 @@
           <t>DA0FS0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="1" t="n">
         <v>0.05633802816901409</v>
       </c>
       <c r="C15" t="n">
@@ -6464,7 +6470,7 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="1" t="n">
         <v>0.7112676056338029</v>
       </c>
       <c r="F15" t="n">
@@ -6488,7 +6494,7 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="1" t="n">
         <v>0.007042253521126761</v>
       </c>
       <c r="N15" t="n">
@@ -6497,13 +6503,13 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="1" t="n">
         <v>0.02816901408450704</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="1" t="n">
         <v>0.02112676056338028</v>
       </c>
       <c r="S15" t="n">
@@ -6539,7 +6545,7 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD15" s="1" t="n">
         <v>0.007042253521126761</v>
       </c>
       <c r="AE15" t="n">
@@ -6569,7 +6575,7 @@
       <c r="AM15" t="n">
         <v>0</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN15" s="1" t="n">
         <v>0.05633802816901409</v>
       </c>
       <c r="AO15" t="n">
@@ -6623,7 +6629,7 @@
       <c r="BE15" t="n">
         <v>0</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BF15" s="1" t="n">
         <v>0.02112676056338028</v>
       </c>
       <c r="BG15" t="n">
@@ -6638,7 +6644,7 @@
       <c r="BJ15" t="n">
         <v>0</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BK15" s="1" t="n">
         <v>0.04225352112676056</v>
       </c>
       <c r="BL15" t="n">
@@ -6689,7 +6695,7 @@
       <c r="CA15" t="n">
         <v>0</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CB15" s="1" t="n">
         <v>0.04929577464788732</v>
       </c>
       <c r="CC15" t="n">
@@ -6867,19 +6873,19 @@
           <t>VSIS3S0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="1" t="n">
         <v>0.04761904761904762</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="1" t="n">
         <v>0.04761904761904762</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="G16" t="n">
@@ -6891,7 +6897,7 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="1" t="n">
         <v>0.3809523809523809</v>
       </c>
       <c r="K16" t="n">
@@ -6900,10 +6906,10 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="1" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="1" t="n">
         <v>0.09523809523809523</v>
       </c>
       <c r="O16" t="n">
@@ -6951,7 +6957,7 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD16" s="1" t="n">
         <v>0.09523809523809523</v>
       </c>
       <c r="AE16" t="n">
@@ -6987,7 +6993,7 @@
       <c r="AO16" t="n">
         <v>0</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP16" s="1" t="n">
         <v>0.09523809523809523</v>
       </c>
       <c r="AQ16" t="n">
@@ -7002,7 +7008,7 @@
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AU16" s="1" t="n">
         <v>0.04761904761904762</v>
       </c>
       <c r="AV16" t="n">
@@ -7279,7 +7285,7 @@
           <t>AQ0CS0</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.0273972602739726</v>
       </c>
       <c r="C17" t="n">
@@ -7288,31 +7294,31 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="1" t="n">
         <v>0.136986301369863</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="1" t="n">
         <v>0.2465753424657534</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="1" t="n">
         <v>0.0958904109589041</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="1" t="n">
         <v>0.0958904109589041</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="N17" t="n">
@@ -7324,7 +7330,7 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="1" t="n">
         <v>0.0273972602739726</v>
       </c>
       <c r="R17" t="n">
@@ -7333,7 +7339,7 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" s="1" t="n">
         <v>0.0821917808219178</v>
       </c>
       <c r="U17" t="n">
@@ -7345,7 +7351,7 @@
       <c r="W17" t="n">
         <v>0</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X17" s="1" t="n">
         <v>0.0410958904109589</v>
       </c>
       <c r="Y17" t="n">
@@ -7363,7 +7369,7 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="AE17" t="n">
@@ -7372,7 +7378,7 @@
       <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="AH17" t="n">
@@ -7381,7 +7387,7 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AJ17" s="1" t="n">
         <v>0.1095890410958904</v>
       </c>
       <c r="AK17" t="n">
@@ -7432,7 +7438,7 @@
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BA17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="BB17" t="n">
@@ -7447,7 +7453,7 @@
       <c r="BE17" t="n">
         <v>0</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BF17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="BG17" t="n">
@@ -7468,7 +7474,7 @@
       <c r="BL17" t="n">
         <v>0</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BM17" s="1" t="n">
         <v>0.0273972602739726</v>
       </c>
       <c r="BN17" t="n">
@@ -7480,7 +7486,7 @@
       <c r="BP17" t="n">
         <v>0</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BQ17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="BR17" t="n">
@@ -7495,7 +7501,7 @@
       <c r="BU17" t="n">
         <v>0</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="BV17" s="1" t="n">
         <v>0.0136986301369863</v>
       </c>
       <c r="BW17" t="n">
@@ -7694,7 +7700,7 @@
       <c r="B18" t="n">
         <v>0</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="D18" t="n">
@@ -7721,7 +7727,7 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="M18" t="n">
@@ -7739,7 +7745,7 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="S18" t="n">
@@ -7760,7 +7766,7 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="Z18" t="n">
@@ -7775,7 +7781,7 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD18" s="1" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="AE18" t="n">
@@ -7784,7 +7790,7 @@
       <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="AH18" t="n">
@@ -7823,7 +7829,7 @@
       <c r="AS18" t="n">
         <v>0</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AT18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="AU18" t="n">
@@ -7838,7 +7844,7 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AY18" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="AZ18" t="n">
@@ -7853,7 +7859,7 @@
       <c r="BC18" t="n">
         <v>0</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BD18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="BE18" t="n">
@@ -7862,7 +7868,7 @@
       <c r="BF18" t="n">
         <v>0</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BG18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="BH18" t="n">
@@ -7904,7 +7910,7 @@
       <c r="BT18" t="n">
         <v>0</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="BU18" s="1" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="BV18" t="n">
@@ -7949,7 +7955,7 @@
       <c r="CI18" t="n">
         <v>0</v>
       </c>
-      <c r="CJ18" t="n">
+      <c r="CJ18" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="CK18" t="n">
@@ -8030,7 +8036,7 @@
       <c r="DJ18" t="n">
         <v>0</v>
       </c>
-      <c r="DK18" t="n">
+      <c r="DK18" s="1" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="DL18" t="n">
@@ -8112,10 +8118,10 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="1" t="n">
         <v>0.1714285714285714</v>
       </c>
       <c r="G19" t="n">
@@ -8130,13 +8136,13 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="1" t="n">
         <v>0.08571428571428572</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="1" t="n">
         <v>0.08571428571428572</v>
       </c>
       <c r="N19" t="n">
@@ -8157,7 +8163,7 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="U19" t="n">
@@ -8172,7 +8178,7 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y19" s="1" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="Z19" t="n">
@@ -8187,7 +8193,7 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD19" s="1" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="AE19" t="n">
@@ -8205,7 +8211,7 @@
       <c r="AI19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AJ19" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AK19" t="n">
@@ -8235,7 +8241,7 @@
       <c r="AS19" t="n">
         <v>0</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AT19" s="1" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="AU19" t="n">
@@ -8265,13 +8271,13 @@
       <c r="BC19" t="n">
         <v>0</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BD19" s="1" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BF19" s="1" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="BG19" t="n">
@@ -8292,7 +8298,7 @@
       <c r="BL19" t="n">
         <v>0</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BM19" s="1" t="n">
         <v>0.02857142857142857</v>
       </c>
       <c r="BN19" t="n">
@@ -8515,7 +8521,7 @@
           <t>Z</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="1" t="n">
         <v>0.07272727272727272</v>
       </c>
       <c r="C20" t="n">
@@ -8542,13 +8548,13 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="1" t="n">
         <v>0.05454545454545454</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
       <c r="N20" t="n">
@@ -8569,7 +8575,7 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
       <c r="U20" t="n">
@@ -8578,7 +8584,7 @@
       <c r="V20" t="n">
         <v>0</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W20" s="1" t="n">
         <v>0.1454545454545454</v>
       </c>
       <c r="X20" t="n">
@@ -8596,7 +8602,7 @@
       <c r="AB20" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC20" s="1" t="n">
         <v>0.3818181818181818</v>
       </c>
       <c r="AD20" t="n">
@@ -8617,7 +8623,7 @@
       <c r="AI20" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AJ20" s="1" t="n">
         <v>0.1272727272727273</v>
       </c>
       <c r="AK20" t="n">
@@ -8641,7 +8647,7 @@
       <c r="AQ20" t="n">
         <v>0</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
       <c r="AS20" t="n">
@@ -8650,7 +8656,7 @@
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AU20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
       <c r="AV20" t="n">
@@ -8662,7 +8668,7 @@
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AY20" s="1" t="n">
         <v>0.07272727272727272</v>
       </c>
       <c r="AZ20" t="n">
@@ -8674,10 +8680,10 @@
       <c r="BB20" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BC20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BD20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
       <c r="BE20" t="n">
@@ -8713,10 +8719,10 @@
       <c r="BO20" t="n">
         <v>0</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BP20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BQ20" s="1" t="n">
         <v>0.01818181818181818</v>
       </c>
       <c r="BR20" t="n">
@@ -8927,31 +8933,31 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="1" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="1" t="n">
         <v>0.01973684210526316</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="1" t="n">
         <v>0.125</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="1" t="n">
         <v>0.03289473684210526</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="K21" t="n">
@@ -8960,25 +8966,25 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="1" t="n">
         <v>0.03289473684210526</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21" s="1" t="n">
         <v>0.01973684210526316</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="T21" t="n">
@@ -8993,10 +8999,10 @@
       <c r="W21" t="n">
         <v>0</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y21" s="1" t="n">
         <v>0.03289473684210526</v>
       </c>
       <c r="Z21" t="n">
@@ -9008,10 +9014,10 @@
       <c r="AB21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC21" s="1" t="n">
         <v>0.01973684210526316</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AD21" s="1" t="n">
         <v>0.1381578947368421</v>
       </c>
       <c r="AE21" t="n">
@@ -9020,7 +9026,7 @@
       <c r="AF21" t="n">
         <v>0</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AG21" s="1" t="n">
         <v>0.01973684210526316</v>
       </c>
       <c r="AH21" t="n">
@@ -9032,7 +9038,7 @@
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AK21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="AL21" t="n">
@@ -9041,31 +9047,31 @@
       <c r="AM21" t="n">
         <v>0</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AN21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AO21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AP21" s="1" t="n">
         <v>0.01973684210526316</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AR21" s="1" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AS21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AT21" s="1" t="n">
         <v>0.03947368421052631</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AU21" s="1" t="n">
         <v>0.01973684210526316</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AV21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="AW21" t="n">
@@ -9074,7 +9080,7 @@
       <c r="AX21" t="n">
         <v>0</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AY21" s="1" t="n">
         <v>0.05921052631578947</v>
       </c>
       <c r="AZ21" t="n">
@@ -9083,28 +9089,28 @@
       <c r="BA21" t="n">
         <v>0</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="BC21" t="n">
         <v>0</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BD21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BE21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BF21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BH21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BI21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="BJ21" t="n">
@@ -9113,7 +9119,7 @@
       <c r="BK21" t="n">
         <v>0</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BL21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="BM21" t="n">
@@ -9134,7 +9140,7 @@
       <c r="BR21" t="n">
         <v>0</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="BS21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="BT21" t="n">
@@ -9152,7 +9158,7 @@
       <c r="BX21" t="n">
         <v>0</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="BY21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="BZ21" t="n">
@@ -9167,7 +9173,7 @@
       <c r="CC21" t="n">
         <v>0</v>
       </c>
-      <c r="CD21" t="n">
+      <c r="CD21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="CE21" t="n">
@@ -9203,7 +9209,7 @@
       <c r="CO21" t="n">
         <v>0</v>
       </c>
-      <c r="CP21" t="n">
+      <c r="CP21" s="1" t="n">
         <v>0.006578947368421052</v>
       </c>
       <c r="CQ21" t="n">
@@ -9260,10 +9266,10 @@
       <c r="DH21" t="n">
         <v>0</v>
       </c>
-      <c r="DI21" t="n">
+      <c r="DI21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="DJ21" t="n">
+      <c r="DJ21" s="1" t="n">
         <v>0.0131578947368421</v>
       </c>
       <c r="DK21" t="n">
@@ -9390,7 +9396,7 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="T22" t="n">
@@ -9399,7 +9405,7 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V22" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="W22" t="n">
@@ -9594,7 +9600,7 @@
       <c r="CH22" t="n">
         <v>0</v>
       </c>
-      <c r="CI22" t="n">
+      <c r="CI22" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CJ22" t="n">
@@ -9769,7 +9775,7 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="I23" t="n">
@@ -9802,7 +9808,7 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="T23" t="n">
@@ -9814,7 +9820,7 @@
       <c r="V23" t="n">
         <v>0</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W23" s="1" t="n">
         <v>0.6111111111111112</v>
       </c>
       <c r="X23" t="n">
@@ -9832,7 +9838,7 @@
       <c r="AB23" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC23" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="AD23" t="n">
@@ -9916,7 +9922,7 @@
       <c r="BD23" t="n">
         <v>0</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BE23" s="1" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="BF23" t="n">
@@ -9928,7 +9934,7 @@
       <c r="BH23" t="n">
         <v>0</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BI23" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="BJ23" t="n">
@@ -10144,7 +10150,7 @@
       <c r="EB23" t="n">
         <v>0</v>
       </c>
-      <c r="EC23" t="n">
+      <c r="EC23" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="ED23" t="n">
@@ -10163,7 +10169,7 @@
           <t>NCFP000</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="1" t="n">
         <v>0.04081632653061224</v>
       </c>
       <c r="C24" t="n">
@@ -10175,7 +10181,7 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="1" t="n">
         <v>0.3877551020408163</v>
       </c>
       <c r="G24" t="n">
@@ -10187,10 +10193,10 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="1" t="n">
         <v>0.1020408163265306</v>
       </c>
       <c r="L24" t="n">
@@ -10217,7 +10223,7 @@
       <c r="S24" t="n">
         <v>0</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="U24" t="n">
@@ -10229,7 +10235,7 @@
       <c r="W24" t="n">
         <v>0</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="Y24" t="n">
@@ -10265,7 +10271,7 @@
       <c r="AI24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AJ24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="AK24" t="n">
@@ -10310,7 +10316,7 @@
       <c r="AX24" t="n">
         <v>0</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AY24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="AZ24" t="n">
@@ -10328,10 +10334,10 @@
       <c r="BD24" t="n">
         <v>0</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BE24" s="1" t="n">
         <v>0.04081632653061224</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BF24" s="1" t="n">
         <v>0.06122448979591837</v>
       </c>
       <c r="BG24" t="n">
@@ -10340,7 +10346,7 @@
       <c r="BH24" t="n">
         <v>0</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BI24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="BJ24" t="n">
@@ -10352,10 +10358,10 @@
       <c r="BL24" t="n">
         <v>0</v>
       </c>
-      <c r="BM24" t="n">
+      <c r="BM24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="BN24" t="n">
+      <c r="BN24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="BO24" t="n">
@@ -10376,7 +10382,7 @@
       <c r="BT24" t="n">
         <v>0</v>
       </c>
-      <c r="BU24" t="n">
+      <c r="BU24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="BV24" t="n">
@@ -10418,7 +10424,7 @@
       <c r="CH24" t="n">
         <v>0</v>
       </c>
-      <c r="CI24" t="n">
+      <c r="CI24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="CJ24" t="n">
@@ -10502,10 +10508,10 @@
       <c r="DJ24" t="n">
         <v>0</v>
       </c>
-      <c r="DK24" t="n">
+      <c r="DK24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="DL24" t="n">
+      <c r="DL24" s="1" t="n">
         <v>0.02040816326530612</v>
       </c>
       <c r="DM24" t="n">
@@ -10575,25 +10581,25 @@
           <t>CS</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="1" t="n">
         <v>0.1414141414141414</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="1" t="n">
         <v>0.0707070707070707</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="1" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="I25" t="n">
@@ -10611,7 +10617,7 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="O25" t="n">
@@ -10620,13 +10626,13 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="T25" t="n">
@@ -10635,40 +10641,40 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AD25" s="1" t="n">
         <v>0.0202020202020202</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="AH25" t="n">
@@ -10677,13 +10683,13 @@
       <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AJ25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AL25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="AM25" t="n">
@@ -10692,28 +10698,28 @@
       <c r="AN25" t="n">
         <v>0</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AO25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AP25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AR25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AS25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AT25" s="1" t="n">
         <v>0.0202020202020202</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AV25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="AW25" t="n">
@@ -10722,7 +10728,7 @@
       <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AY25" s="1" t="n">
         <v>0.04040404040404041</v>
       </c>
       <c r="AZ25" t="n">
@@ -10731,13 +10737,13 @@
       <c r="BA25" t="n">
         <v>0</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB25" s="1" t="n">
         <v>0.0202020202020202</v>
       </c>
       <c r="BC25" t="n">
         <v>0</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BD25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="BE25" t="n">
@@ -10761,13 +10767,13 @@
       <c r="BK25" t="n">
         <v>0</v>
       </c>
-      <c r="BL25" t="n">
+      <c r="BL25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="BM25" t="n">
+      <c r="BM25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="BN25" t="n">
+      <c r="BN25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="BO25" t="n">
@@ -10803,25 +10809,25 @@
       <c r="BY25" t="n">
         <v>0</v>
       </c>
-      <c r="BZ25" t="n">
+      <c r="BZ25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="CA25" t="n">
+      <c r="CA25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="CB25" t="n">
+      <c r="CB25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="CC25" t="n">
         <v>0</v>
       </c>
-      <c r="CD25" t="n">
+      <c r="CD25" s="1" t="n">
         <v>0.04040404040404041</v>
       </c>
       <c r="CE25" t="n">
         <v>0</v>
       </c>
-      <c r="CF25" t="n">
+      <c r="CF25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="CG25" t="n">
@@ -10839,10 +10845,10 @@
       <c r="CK25" t="n">
         <v>0</v>
       </c>
-      <c r="CL25" t="n">
+      <c r="CL25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="CM25" t="n">
+      <c r="CM25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="CN25" t="n">
@@ -10851,7 +10857,7 @@
       <c r="CO25" t="n">
         <v>0</v>
       </c>
-      <c r="CP25" t="n">
+      <c r="CP25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="CQ25" t="n">
@@ -10863,7 +10869,7 @@
       <c r="CS25" t="n">
         <v>0</v>
       </c>
-      <c r="CT25" t="n">
+      <c r="CT25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="CU25" t="n">
@@ -10908,19 +10914,19 @@
       <c r="DH25" t="n">
         <v>0</v>
       </c>
-      <c r="DI25" t="n">
+      <c r="DI25" s="1" t="n">
         <v>0.04040404040404041</v>
       </c>
       <c r="DJ25" t="n">
         <v>0</v>
       </c>
-      <c r="DK25" t="n">
+      <c r="DK25" s="1" t="n">
         <v>0.04040404040404041</v>
       </c>
-      <c r="DL25" t="n">
+      <c r="DL25" s="1" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="DM25" t="n">
+      <c r="DM25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="DN25" t="n">
@@ -10935,7 +10941,7 @@
       <c r="DQ25" t="n">
         <v>0</v>
       </c>
-      <c r="DR25" t="n">
+      <c r="DR25" s="1" t="n">
         <v>0.0101010101010101</v>
       </c>
       <c r="DS25" t="n">
@@ -10993,43 +10999,43 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="1" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="1" t="n">
         <v>0.2318840579710145</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="1" t="n">
         <v>0.05797101449275362</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="1" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="1" t="n">
         <v>0.05797101449275362</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="1" t="n">
         <v>0.04347826086956522</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="Q26" t="n">
@@ -11038,7 +11044,7 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
       <c r="T26" t="n">
@@ -11053,13 +11059,13 @@
       <c r="W26" t="n">
         <v>0</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X26" s="1" t="n">
         <v>0.08695652173913043</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="AA26" t="n">
@@ -11071,25 +11077,25 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AD26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AF26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AG26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AI26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AJ26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
       <c r="AK26" t="n">
@@ -11107,13 +11113,13 @@
       <c r="AO26" t="n">
         <v>0</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AP26" s="1" t="n">
         <v>0.04347826086956522</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AR26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="AS26" t="n">
@@ -11122,7 +11128,7 @@
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AU26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="AV26" t="n">
@@ -11143,7 +11149,7 @@
       <c r="BA26" t="n">
         <v>0</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BB26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="BC26" t="n">
@@ -11161,7 +11167,7 @@
       <c r="BG26" t="n">
         <v>0</v>
       </c>
-      <c r="BH26" t="n">
+      <c r="BH26" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="BI26" t="n">
@@ -11173,10 +11179,10 @@
       <c r="BK26" t="n">
         <v>0</v>
       </c>
-      <c r="BL26" t="n">
+      <c r="BL26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="BM26" t="n">
+      <c r="BM26" s="1" t="n">
         <v>0.04347826086956522</v>
       </c>
       <c r="BN26" t="n">
@@ -11266,7 +11272,7 @@
       <c r="CP26" t="n">
         <v>0</v>
       </c>
-      <c r="CQ26" t="n">
+      <c r="CQ26" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
       <c r="CR26" t="n">
@@ -11408,7 +11414,7 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="F27" t="n">
@@ -11417,13 +11423,13 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="1" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="K27" t="n">
@@ -11432,7 +11438,7 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="N27" t="n">
@@ -11441,7 +11447,7 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="Q27" t="n">
@@ -11474,7 +11480,7 @@
       <c r="Z27" t="n">
         <v>0</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AA27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AB27" t="n">
@@ -11486,7 +11492,7 @@
       <c r="AD27" t="n">
         <v>0</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AE27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AF27" t="n">
@@ -11633,7 +11639,7 @@
       <c r="CA27" t="n">
         <v>0</v>
       </c>
-      <c r="CB27" t="n">
+      <c r="CB27" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="CC27" t="n">
@@ -11823,7 +11829,7 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="G28" t="n">
@@ -11895,7 +11901,7 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AD28" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AE28" t="n">
@@ -12105,7 +12111,7 @@
       <c r="CU28" t="n">
         <v>0</v>
       </c>
-      <c r="CV28" t="n">
+      <c r="CV28" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CW28" t="n">
@@ -12274,7 +12280,7 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="T29" t="n">
@@ -12304,7 +12310,7 @@
       <c r="AB29" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC29" s="1" t="n">
         <v>0.6</v>
       </c>
       <c r="AD29" t="n">
@@ -12526,7 +12532,7 @@
       <c r="CX29" t="n">
         <v>0</v>
       </c>
-      <c r="CY29" t="n">
+      <c r="CY29" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="CZ29" t="n">
@@ -12635,7 +12641,7 @@
           <t>NCMP000</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="C30" t="n">
@@ -12647,7 +12653,7 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="1" t="n">
         <v>0.34375</v>
       </c>
       <c r="G30" t="n">
@@ -12662,7 +12668,7 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="1" t="n">
         <v>0.0859375</v>
       </c>
       <c r="L30" t="n">
@@ -12680,16 +12686,16 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="1" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" s="1" t="n">
         <v>0.046875</v>
       </c>
       <c r="U30" t="n">
@@ -12701,10 +12707,10 @@
       <c r="W30" t="n">
         <v>0</v>
       </c>
-      <c r="X30" t="n">
+      <c r="X30" s="1" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Y30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="Z30" t="n">
@@ -12716,19 +12722,19 @@
       <c r="AB30" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AC30" s="1" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AD30" s="1" t="n">
         <v>0.03125</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE30" s="1" t="n">
         <v>0.0390625</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="AH30" t="n">
@@ -12737,7 +12743,7 @@
       <c r="AI30" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AJ30" s="1" t="n">
         <v>0.140625</v>
       </c>
       <c r="AK30" t="n">
@@ -12773,7 +12779,7 @@
       <c r="AU30" t="n">
         <v>0</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AV30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="AW30" t="n">
@@ -12782,7 +12788,7 @@
       <c r="AX30" t="n">
         <v>0</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AY30" s="1" t="n">
         <v>0.015625</v>
       </c>
       <c r="AZ30" t="n">
@@ -12797,13 +12803,13 @@
       <c r="BC30" t="n">
         <v>0</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BD30" s="1" t="n">
         <v>0.0390625</v>
       </c>
       <c r="BE30" t="n">
         <v>0</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BF30" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="BG30" t="n">
@@ -12812,19 +12818,19 @@
       <c r="BH30" t="n">
         <v>0</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BI30" s="1" t="n">
         <v>0.0234375</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BJ30" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="BK30" t="n">
         <v>0</v>
       </c>
-      <c r="BL30" t="n">
+      <c r="BL30" s="1" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="BM30" t="n">
+      <c r="BM30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="BN30" t="n">
@@ -12833,10 +12839,10 @@
       <c r="BO30" t="n">
         <v>0</v>
       </c>
-      <c r="BP30" t="n">
+      <c r="BP30" s="1" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="BQ30" t="n">
+      <c r="BQ30" s="1" t="n">
         <v>0.015625</v>
       </c>
       <c r="BR30" t="n">
@@ -12899,7 +12905,7 @@
       <c r="CK30" t="n">
         <v>0</v>
       </c>
-      <c r="CL30" t="n">
+      <c r="CL30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="CM30" t="n">
@@ -12965,7 +12971,7 @@
       <c r="DG30" t="n">
         <v>0</v>
       </c>
-      <c r="DH30" t="n">
+      <c r="DH30" s="1" t="n">
         <v>0.015625</v>
       </c>
       <c r="DI30" t="n">
@@ -13001,7 +13007,7 @@
       <c r="DS30" t="n">
         <v>0</v>
       </c>
-      <c r="DT30" t="n">
+      <c r="DT30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="DU30" t="n">
@@ -13019,7 +13025,7 @@
       <c r="DY30" t="n">
         <v>0</v>
       </c>
-      <c r="DZ30" t="n">
+      <c r="DZ30" s="1" t="n">
         <v>0.0078125</v>
       </c>
       <c r="EA30" t="n">
@@ -13047,10 +13053,10 @@
           <t>RG</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
       <c r="D31" t="n">
@@ -13059,7 +13065,7 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="1" t="n">
         <v>0.1732283464566929</v>
       </c>
       <c r="G31" t="n">
@@ -13068,16 +13074,16 @@
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="1" t="n">
         <v>0.02362204724409449</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="1" t="n">
         <v>0.03149606299212598</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="1" t="n">
         <v>0.04724409448818898</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="1" t="n">
         <v>0.02362204724409449</v>
       </c>
       <c r="M31" t="n">
@@ -13089,19 +13095,19 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31" s="1" t="n">
         <v>0.03937007874015748</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R31" s="1" t="n">
         <v>0.03149606299212598</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" s="1" t="n">
         <v>0.03149606299212598</v>
       </c>
       <c r="U31" t="n">
@@ -13113,10 +13119,10 @@
       <c r="W31" t="n">
         <v>0</v>
       </c>
-      <c r="X31" t="n">
+      <c r="X31" s="1" t="n">
         <v>0.02362204724409449</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y31" s="1" t="n">
         <v>0.03149606299212598</v>
       </c>
       <c r="Z31" t="n">
@@ -13128,28 +13134,28 @@
       <c r="AB31" t="n">
         <v>0</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AC31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AD31" s="1" t="n">
         <v>0.05511811023622047</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AF31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AH31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AJ31" s="1" t="n">
         <v>0.1417322834645669</v>
       </c>
       <c r="AK31" t="n">
@@ -13167,7 +13173,7 @@
       <c r="AO31" t="n">
         <v>0</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AP31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="AQ31" t="n">
@@ -13179,13 +13185,13 @@
       <c r="AS31" t="n">
         <v>0</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AT31" s="1" t="n">
         <v>0.03937007874015748</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AU31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AV31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="AW31" t="n">
@@ -13194,7 +13200,7 @@
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AY31" s="1" t="n">
         <v>0.05511811023622047</v>
       </c>
       <c r="AZ31" t="n">
@@ -13203,7 +13209,7 @@
       <c r="BA31" t="n">
         <v>0</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="BC31" t="n">
@@ -13215,7 +13221,7 @@
       <c r="BE31" t="n">
         <v>0</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BF31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="BG31" t="n">
@@ -13224,7 +13230,7 @@
       <c r="BH31" t="n">
         <v>0</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BI31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="BJ31" t="n">
@@ -13236,7 +13242,7 @@
       <c r="BL31" t="n">
         <v>0</v>
       </c>
-      <c r="BM31" t="n">
+      <c r="BM31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="BN31" t="n">
@@ -13263,7 +13269,7 @@
       <c r="BU31" t="n">
         <v>0</v>
       </c>
-      <c r="BV31" t="n">
+      <c r="BV31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="BW31" t="n">
@@ -13314,7 +13320,7 @@
       <c r="CL31" t="n">
         <v>0</v>
       </c>
-      <c r="CM31" t="n">
+      <c r="CM31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="CN31" t="n">
@@ -13323,7 +13329,7 @@
       <c r="CO31" t="n">
         <v>0</v>
       </c>
-      <c r="CP31" t="n">
+      <c r="CP31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="CQ31" t="n">
@@ -13332,7 +13338,7 @@
       <c r="CR31" t="n">
         <v>0</v>
       </c>
-      <c r="CS31" t="n">
+      <c r="CS31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="CT31" t="n">
@@ -13344,7 +13350,7 @@
       <c r="CV31" t="n">
         <v>0</v>
       </c>
-      <c r="CW31" t="n">
+      <c r="CW31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="CX31" t="n">
@@ -13356,13 +13362,13 @@
       <c r="CZ31" t="n">
         <v>0</v>
       </c>
-      <c r="DA31" t="n">
+      <c r="DA31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="DB31" t="n">
         <v>0</v>
       </c>
-      <c r="DC31" t="n">
+      <c r="DC31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="DD31" t="n">
@@ -13377,10 +13383,10 @@
       <c r="DG31" t="n">
         <v>0</v>
       </c>
-      <c r="DH31" t="n">
+      <c r="DH31" s="1" t="n">
         <v>0.01574803149606299</v>
       </c>
-      <c r="DI31" t="n">
+      <c r="DI31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="DJ31" t="n">
@@ -13389,7 +13395,7 @@
       <c r="DK31" t="n">
         <v>0</v>
       </c>
-      <c r="DL31" t="n">
+      <c r="DL31" s="1" t="n">
         <v>0.007874015748031496</v>
       </c>
       <c r="DM31" t="n">
@@ -13471,7 +13477,7 @@
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="1" t="n">
         <v>0.6153846153846154</v>
       </c>
       <c r="G32" t="n">
@@ -13486,7 +13492,7 @@
       <c r="J32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="1" t="n">
         <v>0.1538461538461539</v>
       </c>
       <c r="L32" t="n">
@@ -13525,7 +13531,7 @@
       <c r="W32" t="n">
         <v>0</v>
       </c>
-      <c r="X32" t="n">
+      <c r="X32" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="Y32" t="n">
@@ -13561,7 +13567,7 @@
       <c r="AI32" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AJ32" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="AK32" t="n">
@@ -13615,7 +13621,7 @@
       <c r="BA32" t="n">
         <v>0</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB32" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="BC32" t="n">
@@ -13922,7 +13928,7 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="T33" t="n">
@@ -13931,10 +13937,10 @@
       <c r="U33" t="n">
         <v>0</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V33" s="1" t="n">
         <v>0.125</v>
       </c>
-      <c r="W33" t="n">
+      <c r="W33" s="1" t="n">
         <v>0.75</v>
       </c>
       <c r="X33" t="n">
@@ -14289,28 +14295,28 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="1" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="1" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="1" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="1" t="n">
         <v>0.05681818181818182</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="1" t="n">
         <v>0.03409090909090909</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="1" t="n">
         <v>0.03409090909090909</v>
       </c>
       <c r="L34" t="n">
@@ -14319,7 +14325,7 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="1" t="n">
         <v>0.04545454545454546</v>
       </c>
       <c r="O34" t="n">
@@ -14334,22 +14340,22 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" s="1" t="n">
         <v>0.03409090909090909</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
-      <c r="W34" t="n">
+      <c r="W34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
-      <c r="X34" t="n">
+      <c r="X34" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="Y34" t="n">
@@ -14364,28 +14370,28 @@
       <c r="AB34" t="n">
         <v>0</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AC34" s="1" t="n">
         <v>0.05681818181818182</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AD34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AE34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AG34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AJ34" s="1" t="n">
         <v>0.03409090909090909</v>
       </c>
       <c r="AK34" t="n">
@@ -14400,16 +14406,16 @@
       <c r="AN34" t="n">
         <v>0</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AO34" s="1" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AP34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AR34" s="1" t="n">
         <v>0.03409090909090909</v>
       </c>
       <c r="AS34" t="n">
@@ -14418,7 +14424,7 @@
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AU34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="AV34" t="n">
@@ -14439,7 +14445,7 @@
       <c r="BA34" t="n">
         <v>0</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="BC34" t="n">
@@ -14472,13 +14478,13 @@
       <c r="BL34" t="n">
         <v>0</v>
       </c>
-      <c r="BM34" t="n">
+      <c r="BM34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="BN34" t="n">
         <v>0</v>
       </c>
-      <c r="BO34" t="n">
+      <c r="BO34" s="1" t="n">
         <v>0.05681818181818182</v>
       </c>
       <c r="BP34" t="n">
@@ -14514,7 +14520,7 @@
       <c r="BZ34" t="n">
         <v>0</v>
       </c>
-      <c r="CA34" t="n">
+      <c r="CA34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="CB34" t="n">
@@ -14523,7 +14529,7 @@
       <c r="CC34" t="n">
         <v>0</v>
       </c>
-      <c r="CD34" t="n">
+      <c r="CD34" s="1" t="n">
         <v>0.02272727272727273</v>
       </c>
       <c r="CE34" t="n">
@@ -14550,7 +14556,7 @@
       <c r="CL34" t="n">
         <v>0</v>
       </c>
-      <c r="CM34" t="n">
+      <c r="CM34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="CN34" t="n">
@@ -14619,7 +14625,7 @@
       <c r="DI34" t="n">
         <v>0</v>
       </c>
-      <c r="DJ34" t="n">
+      <c r="DJ34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="DK34" t="n">
@@ -14661,7 +14667,7 @@
       <c r="DW34" t="n">
         <v>0</v>
       </c>
-      <c r="DX34" t="n">
+      <c r="DX34" s="1" t="n">
         <v>0.01136363636363636</v>
       </c>
       <c r="DY34" t="n">
@@ -14725,7 +14731,7 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="M35" t="n">
@@ -14794,7 +14800,7 @@
       <c r="AH35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AI35" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AJ35" t="n">
@@ -14827,7 +14833,7 @@
       <c r="AS35" t="n">
         <v>0</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AT35" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AU35" t="n">
@@ -15034,7 +15040,7 @@
       <c r="DJ35" t="n">
         <v>0</v>
       </c>
-      <c r="DK35" t="n">
+      <c r="DK35" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="DL35" t="n">
@@ -15107,13 +15113,13 @@
           <t>Fd</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="1" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="1" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="E36" t="n">
@@ -15143,7 +15149,7 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="O36" t="n">
@@ -15239,7 +15245,7 @@
       <c r="AS36" t="n">
         <v>0</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AT36" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AU36" t="n">
@@ -15296,7 +15302,7 @@
       <c r="BL36" t="n">
         <v>0</v>
       </c>
-      <c r="BM36" t="n">
+      <c r="BM36" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="BN36" t="n">
@@ -15305,7 +15311,7 @@
       <c r="BO36" t="n">
         <v>0</v>
       </c>
-      <c r="BP36" t="n">
+      <c r="BP36" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="BQ36" t="n">
@@ -15425,7 +15431,7 @@
       <c r="DC36" t="n">
         <v>0</v>
       </c>
-      <c r="DD36" t="n">
+      <c r="DD36" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="DE36" t="n">
@@ -15519,31 +15525,31 @@
           <t>Fc</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="1" t="n">
         <v>0.1553398058252427</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="1" t="n">
         <v>0.01941747572815534</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="1" t="n">
         <v>0.01941747572815534</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="1" t="n">
         <v>0.01456310679611651</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="1" t="n">
         <v>0.1699029126213592</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="1" t="n">
         <v>0.03883495145631068</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="1" t="n">
         <v>0.01456310679611651</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="1" t="n">
         <v>0.01456310679611651</v>
       </c>
       <c r="K37" t="n">
@@ -15552,19 +15558,19 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="1" t="n">
         <v>0.009708737864077669</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="1" t="n">
         <v>0.03398058252427184</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="1" t="n">
         <v>0.009708737864077669</v>
       </c>
       <c r="R37" t="n">
@@ -15573,22 +15579,22 @@
       <c r="S37" t="n">
         <v>0</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" s="1" t="n">
         <v>0.1067961165048544</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
-      <c r="V37" t="n">
+      <c r="V37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
-      <c r="X37" t="n">
+      <c r="X37" s="1" t="n">
         <v>0.06310679611650485</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y37" s="1" t="n">
         <v>0.01456310679611651</v>
       </c>
       <c r="Z37" t="n">
@@ -15603,7 +15609,7 @@
       <c r="AC37" t="n">
         <v>0</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AD37" s="1" t="n">
         <v>0.03883495145631068</v>
       </c>
       <c r="AE37" t="n">
@@ -15636,25 +15642,25 @@
       <c r="AN37" t="n">
         <v>0</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AO37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AP37" s="1" t="n">
         <v>0.01941747572815534</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AR37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="AS37" t="n">
         <v>0</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AT37" s="1" t="n">
         <v>0.02912621359223301</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AU37" s="1" t="n">
         <v>0.05339805825242718</v>
       </c>
       <c r="AV37" t="n">
@@ -15663,10 +15669,10 @@
       <c r="AW37" t="n">
         <v>0</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AX37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AY37" s="1" t="n">
         <v>0.01941747572815534</v>
       </c>
       <c r="AZ37" t="n">
@@ -15675,16 +15681,16 @@
       <c r="BA37" t="n">
         <v>0</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB37" s="1" t="n">
         <v>0.01456310679611651</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BD37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BE37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="BF37" t="n">
@@ -15693,7 +15699,7 @@
       <c r="BG37" t="n">
         <v>0</v>
       </c>
-      <c r="BH37" t="n">
+      <c r="BH37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="BI37" t="n">
@@ -15702,13 +15708,13 @@
       <c r="BJ37" t="n">
         <v>0</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BK37" s="1" t="n">
         <v>0.02427184466019417</v>
       </c>
-      <c r="BL37" t="n">
+      <c r="BL37" s="1" t="n">
         <v>0.009708737864077669</v>
       </c>
-      <c r="BM37" t="n">
+      <c r="BM37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="BN37" t="n">
@@ -15723,13 +15729,13 @@
       <c r="BQ37" t="n">
         <v>0</v>
       </c>
-      <c r="BR37" t="n">
+      <c r="BR37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="BS37" t="n">
         <v>0</v>
       </c>
-      <c r="BT37" t="n">
+      <c r="BT37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="BU37" t="n">
@@ -15783,10 +15789,10 @@
       <c r="CK37" t="n">
         <v>0</v>
       </c>
-      <c r="CL37" t="n">
+      <c r="CL37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
-      <c r="CM37" t="n">
+      <c r="CM37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="CN37" t="n">
@@ -15795,7 +15801,7 @@
       <c r="CO37" t="n">
         <v>0</v>
       </c>
-      <c r="CP37" t="n">
+      <c r="CP37" s="1" t="n">
         <v>0.009708737864077669</v>
       </c>
       <c r="CQ37" t="n">
@@ -15819,7 +15825,7 @@
       <c r="CW37" t="n">
         <v>0</v>
       </c>
-      <c r="CX37" t="n">
+      <c r="CX37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="CY37" t="n">
@@ -15831,7 +15837,7 @@
       <c r="DA37" t="n">
         <v>0</v>
       </c>
-      <c r="DB37" t="n">
+      <c r="DB37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="DC37" t="n">
@@ -15852,13 +15858,13 @@
       <c r="DH37" t="n">
         <v>0</v>
       </c>
-      <c r="DI37" t="n">
+      <c r="DI37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="DJ37" t="n">
         <v>0</v>
       </c>
-      <c r="DK37" t="n">
+      <c r="DK37" s="1" t="n">
         <v>0.004854368932038835</v>
       </c>
       <c r="DL37" t="n">
@@ -15873,7 +15879,7 @@
       <c r="DO37" t="n">
         <v>0</v>
       </c>
-      <c r="DP37" t="n">
+      <c r="DP37" s="1" t="n">
         <v>0.009708737864077669</v>
       </c>
       <c r="DQ37" t="n">
@@ -15943,7 +15949,7 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
@@ -16454,7 +16460,7 @@
       <c r="AL39" t="n">
         <v>0</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AM39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AN39" t="n">
@@ -16779,7 +16785,7 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K40" t="n">
@@ -16788,7 +16794,7 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="N40" t="n">
@@ -17176,7 +17182,7 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="1" t="n">
         <v>0.75</v>
       </c>
       <c r="F41" t="n">
@@ -17206,7 +17212,7 @@
       <c r="N41" t="n">
         <v>0</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="P41" t="n">
@@ -17221,7 +17227,7 @@
       <c r="S41" t="n">
         <v>0</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="U41" t="n">
@@ -17642,7 +17648,7 @@
       <c r="V42" t="n">
         <v>0</v>
       </c>
-      <c r="W42" t="n">
+      <c r="W42" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="X42" t="n">
@@ -17660,7 +17666,7 @@
       <c r="AB42" t="n">
         <v>0</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AC42" s="1" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="AD42" t="n">
@@ -17738,7 +17744,7 @@
       <c r="BB42" t="n">
         <v>0</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BC42" s="1" t="n">
         <v>0.1111111111111111</v>
       </c>
       <c r="BD42" t="n">
@@ -17759,7 +17765,7 @@
       <c r="BI42" t="n">
         <v>0</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BJ42" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="BK42" t="n">
@@ -17991,7 +17997,7 @@
           <t>DI0MS0</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="1" t="n">
         <v>0.09230769230769231</v>
       </c>
       <c r="C43" t="n">
@@ -18000,22 +18006,22 @@
       <c r="D43" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="1" t="n">
         <v>0.01538461538461539</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="1" t="n">
         <v>0.03076923076923077</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="1" t="n">
         <v>0.06153846153846154</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="1" t="n">
         <v>0.01538461538461539</v>
       </c>
       <c r="K43" t="n">
@@ -18033,7 +18039,7 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43" s="1" t="n">
         <v>0.04615384615384616</v>
       </c>
       <c r="Q43" t="n">
@@ -18066,7 +18072,7 @@
       <c r="Z43" t="n">
         <v>0</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AA43" s="1" t="n">
         <v>0.01538461538461539</v>
       </c>
       <c r="AB43" t="n">
@@ -18144,7 +18150,7 @@
       <c r="AZ43" t="n">
         <v>0</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BA43" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="BB43" t="n">
@@ -18168,7 +18174,7 @@
       <c r="BH43" t="n">
         <v>0</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BI43" s="1" t="n">
         <v>0.01538461538461539</v>
       </c>
       <c r="BJ43" t="n">
@@ -18225,7 +18231,7 @@
       <c r="CA43" t="n">
         <v>0</v>
       </c>
-      <c r="CB43" t="n">
+      <c r="CB43" s="1" t="n">
         <v>0.01538461538461539</v>
       </c>
       <c r="CC43" t="n">
@@ -18252,7 +18258,7 @@
       <c r="CJ43" t="n">
         <v>0</v>
       </c>
-      <c r="CK43" t="n">
+      <c r="CK43" s="1" t="n">
         <v>0.01538461538461539</v>
       </c>
       <c r="CL43" t="n">
@@ -18412,7 +18418,7 @@
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
@@ -18824,22 +18830,22 @@
       <c r="D45" t="n">
         <v>0</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="1" t="n">
         <v>0.5245901639344263</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="1" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="1" t="n">
         <v>0.3114754098360656</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="1" t="n">
         <v>0.04918032786885246</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="1" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="K45" t="n">
@@ -18857,7 +18863,7 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45" s="1" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="Q45" t="n">
@@ -19004,7 +19010,7 @@
       <c r="BL45" t="n">
         <v>0</v>
       </c>
-      <c r="BM45" t="n">
+      <c r="BM45" s="1" t="n">
         <v>0.03278688524590164</v>
       </c>
       <c r="BN45" t="n">
@@ -19040,7 +19046,7 @@
       <c r="BX45" t="n">
         <v>0</v>
       </c>
-      <c r="BY45" t="n">
+      <c r="BY45" s="1" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="BZ45" t="n">
@@ -19142,7 +19148,7 @@
       <c r="DF45" t="n">
         <v>0</v>
       </c>
-      <c r="DG45" t="n">
+      <c r="DG45" s="1" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="DH45" t="n">
@@ -19359,7 +19365,7 @@
       <c r="AS46" t="n">
         <v>0</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AT46" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="AU46" t="n">
@@ -19374,7 +19380,7 @@
       <c r="AX46" t="n">
         <v>0</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="AY46" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AZ46" t="n">
@@ -19566,7 +19572,7 @@
       <c r="DJ46" t="n">
         <v>0</v>
       </c>
-      <c r="DK46" t="n">
+      <c r="DK46" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="DL46" t="n">
@@ -19639,43 +19645,43 @@
           <t>VMIP3S0</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="1" t="n">
         <v>0.02238805970149254</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="1" t="n">
         <v>0.02985074626865672</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="1" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="1" t="n">
         <v>0.2835820895522388</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="1" t="n">
         <v>0.03731343283582089</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="1" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="1" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47" s="1" t="n">
         <v>0.02238805970149254</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47" s="1" t="n">
         <v>0.05970149253731343</v>
       </c>
       <c r="O47" t="n">
@@ -19687,13 +19693,13 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R47" s="1" t="n">
         <v>0.01492537313432836</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T47" s="1" t="n">
         <v>0.02985074626865672</v>
       </c>
       <c r="U47" t="n">
@@ -19702,16 +19708,16 @@
       <c r="V47" t="n">
         <v>0</v>
       </c>
-      <c r="W47" t="n">
+      <c r="W47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="X47" t="n">
+      <c r="X47" s="1" t="n">
         <v>0.07462686567164178</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="Z47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="AA47" t="n">
@@ -19720,19 +19726,19 @@
       <c r="AB47" t="n">
         <v>0</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AC47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AD47" s="1" t="n">
         <v>0.05970149253731343</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AF47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AG47" s="1" t="n">
         <v>0.07462686567164178</v>
       </c>
       <c r="AH47" t="n">
@@ -19741,7 +19747,7 @@
       <c r="AI47" t="n">
         <v>0</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AJ47" s="1" t="n">
         <v>0.03731343283582089</v>
       </c>
       <c r="AK47" t="n">
@@ -19759,22 +19765,22 @@
       <c r="AO47" t="n">
         <v>0</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AP47" s="1" t="n">
         <v>0.03731343283582089</v>
       </c>
       <c r="AQ47" t="n">
         <v>0</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AR47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="AS47" t="n">
         <v>0</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AT47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AU47" s="1" t="n">
         <v>0.03731343283582089</v>
       </c>
       <c r="AV47" t="n">
@@ -19783,7 +19789,7 @@
       <c r="AW47" t="n">
         <v>0</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AX47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="AY47" t="n">
@@ -19795,7 +19801,7 @@
       <c r="BA47" t="n">
         <v>0</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BB47" s="1" t="n">
         <v>0.01492537313432836</v>
       </c>
       <c r="BC47" t="n">
@@ -19804,7 +19810,7 @@
       <c r="BD47" t="n">
         <v>0</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BE47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="BF47" t="n">
@@ -19828,7 +19834,7 @@
       <c r="BL47" t="n">
         <v>0</v>
       </c>
-      <c r="BM47" t="n">
+      <c r="BM47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="BN47" t="n">
@@ -19843,7 +19849,7 @@
       <c r="BQ47" t="n">
         <v>0</v>
       </c>
-      <c r="BR47" t="n">
+      <c r="BR47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="BS47" t="n">
@@ -19903,7 +19909,7 @@
       <c r="CK47" t="n">
         <v>0</v>
       </c>
-      <c r="CL47" t="n">
+      <c r="CL47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="CM47" t="n">
@@ -19987,7 +19993,7 @@
       <c r="DM47" t="n">
         <v>0</v>
       </c>
-      <c r="DN47" t="n">
+      <c r="DN47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="DO47" t="n">
@@ -20008,7 +20014,7 @@
       <c r="DT47" t="n">
         <v>0</v>
       </c>
-      <c r="DU47" t="n">
+      <c r="DU47" s="1" t="n">
         <v>0.007462686567164179</v>
       </c>
       <c r="DV47" t="n">
@@ -20063,13 +20069,13 @@
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="1" t="n">
         <v>0.3125</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="1" t="n">
         <v>0.03125</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="I48" t="n">
@@ -20087,7 +20093,7 @@
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="O48" t="n">
@@ -20114,10 +20120,10 @@
       <c r="V48" t="n">
         <v>0</v>
       </c>
-      <c r="W48" t="n">
+      <c r="W48" s="1" t="n">
         <v>0.03125</v>
       </c>
-      <c r="X48" t="n">
+      <c r="X48" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="Y48" t="n">
@@ -20132,7 +20138,7 @@
       <c r="AB48" t="n">
         <v>0</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AC48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="AD48" t="n">
@@ -20141,7 +20147,7 @@
       <c r="AE48" t="n">
         <v>0</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AF48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="AG48" t="n">
@@ -20153,7 +20159,7 @@
       <c r="AI48" t="n">
         <v>0</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AJ48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="AK48" t="n">
@@ -20168,7 +20174,7 @@
       <c r="AN48" t="n">
         <v>0</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AO48" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="AP48" t="n">
@@ -20177,7 +20183,7 @@
       <c r="AQ48" t="n">
         <v>0</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AR48" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="AS48" t="n">
@@ -20189,7 +20195,7 @@
       <c r="AU48" t="n">
         <v>0</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AV48" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="AW48" t="n">
@@ -20207,7 +20213,7 @@
       <c r="BA48" t="n">
         <v>0</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BB48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="BC48" t="n">
@@ -20222,7 +20228,7 @@
       <c r="BF48" t="n">
         <v>0</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BG48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="BH48" t="n">
@@ -20231,7 +20237,7 @@
       <c r="BI48" t="n">
         <v>0</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BJ48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="BK48" t="n">
@@ -20246,7 +20252,7 @@
       <c r="BN48" t="n">
         <v>0</v>
       </c>
-      <c r="BO48" t="n">
+      <c r="BO48" s="1" t="n">
         <v>0.09375</v>
       </c>
       <c r="BP48" t="n">
@@ -20282,7 +20288,7 @@
       <c r="BZ48" t="n">
         <v>0</v>
       </c>
-      <c r="CA48" t="n">
+      <c r="CA48" s="1" t="n">
         <v>0.03125</v>
       </c>
       <c r="CB48" t="n">
@@ -20484,16 +20490,16 @@
       <c r="H49" t="n">
         <v>0</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="M49" t="n">
@@ -20532,7 +20538,7 @@
       <c r="X49" t="n">
         <v>0</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="Z49" t="n">
@@ -20595,7 +20601,7 @@
       <c r="AS49" t="n">
         <v>0</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AT49" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AU49" t="n">
@@ -20625,7 +20631,7 @@
       <c r="BC49" t="n">
         <v>0</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BD49" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="BE49" t="n">
@@ -20709,7 +20715,7 @@
       <c r="CE49" t="n">
         <v>0</v>
       </c>
-      <c r="CF49" t="n">
+      <c r="CF49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="CG49" t="n">
@@ -20721,7 +20727,7 @@
       <c r="CI49" t="n">
         <v>0</v>
       </c>
-      <c r="CJ49" t="n">
+      <c r="CJ49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="CK49" t="n">
@@ -20736,7 +20742,7 @@
       <c r="CN49" t="n">
         <v>0</v>
       </c>
-      <c r="CO49" t="n">
+      <c r="CO49" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="CP49" t="n">
@@ -20887,7 +20893,7 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
@@ -21287,7 +21293,7 @@
           <t>DD0MS0</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="C51" t="n">
@@ -21305,13 +21311,13 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="1" t="n">
         <v>0.8461538461538461</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="K51" t="n">
@@ -21768,7 +21774,7 @@
       <c r="X52" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Y52" s="1" t="n">
         <v>0.2318840579710145</v>
       </c>
       <c r="Z52" t="n">
@@ -21831,13 +21837,13 @@
       <c r="AS52" t="n">
         <v>0</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AT52" s="1" t="n">
         <v>0.3768115942028986</v>
       </c>
       <c r="AU52" t="n">
         <v>0</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AV52" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="AW52" t="n">
@@ -21861,7 +21867,7 @@
       <c r="BC52" t="n">
         <v>0</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BD52" s="1" t="n">
         <v>0.2173913043478261</v>
       </c>
       <c r="BE52" t="n">
@@ -21888,7 +21894,7 @@
       <c r="BL52" t="n">
         <v>0</v>
       </c>
-      <c r="BM52" t="n">
+      <c r="BM52" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="BN52" t="n">
@@ -21903,7 +21909,7 @@
       <c r="BQ52" t="n">
         <v>0</v>
       </c>
-      <c r="BR52" t="n">
+      <c r="BR52" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="BS52" t="n">
@@ -21939,10 +21945,10 @@
       <c r="CC52" t="n">
         <v>0</v>
       </c>
-      <c r="CD52" t="n">
+      <c r="CD52" s="1" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="CE52" t="n">
+      <c r="CE52" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="CF52" t="n">
@@ -21957,7 +21963,7 @@
       <c r="CI52" t="n">
         <v>0</v>
       </c>
-      <c r="CJ52" t="n">
+      <c r="CJ52" s="1" t="n">
         <v>0.02898550724637681</v>
       </c>
       <c r="CK52" t="n">
@@ -22038,7 +22044,7 @@
       <c r="DJ52" t="n">
         <v>0</v>
       </c>
-      <c r="DK52" t="n">
+      <c r="DK52" s="1" t="n">
         <v>0.01449275362318841</v>
       </c>
       <c r="DL52" t="n">
@@ -22111,7 +22117,7 @@
           <t>W</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="1" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="C53" t="n">
@@ -22123,7 +22129,7 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="1" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="G53" t="n">
@@ -22138,7 +22144,7 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53" s="1" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="L53" t="n">
@@ -22213,7 +22219,7 @@
       <c r="AI53" t="n">
         <v>0</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AJ53" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="AK53" t="n">
@@ -22249,7 +22255,7 @@
       <c r="AU53" t="n">
         <v>0</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AV53" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="AW53" t="n">
@@ -22258,7 +22264,7 @@
       <c r="AX53" t="n">
         <v>0</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="AY53" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="AZ53" t="n">
@@ -22312,7 +22318,7 @@
       <c r="BP53" t="n">
         <v>0</v>
       </c>
-      <c r="BQ53" t="n">
+      <c r="BQ53" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="BR53" t="n">
@@ -22483,7 +22489,7 @@
       <c r="DU53" t="n">
         <v>0</v>
       </c>
-      <c r="DV53" t="n">
+      <c r="DV53" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="DW53" t="n">
@@ -22544,13 +22550,13 @@
       <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="L54" t="n">
@@ -22565,7 +22571,7 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P54" s="1" t="n">
         <v>0.3846153846153846</v>
       </c>
       <c r="Q54" t="n">
@@ -22577,7 +22583,7 @@
       <c r="S54" t="n">
         <v>0</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T54" s="1" t="n">
         <v>0.1538461538461539</v>
       </c>
       <c r="U54" t="n">
@@ -22658,7 +22664,7 @@
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AU54" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="AV54" t="n">
@@ -22670,7 +22676,7 @@
       <c r="AX54" t="n">
         <v>0</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="AY54" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="AZ54" t="n">
@@ -22691,7 +22697,7 @@
       <c r="BE54" t="n">
         <v>0</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BF54" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="BG54" t="n">
@@ -22739,7 +22745,7 @@
       <c r="BU54" t="n">
         <v>0</v>
       </c>
-      <c r="BV54" t="n">
+      <c r="BV54" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="BW54" t="n">
@@ -22935,7 +22941,7 @@
           <t>DA0MP0</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="1" t="n">
         <v>0.02272727272727273</v>
       </c>
       <c r="C55" t="n">
@@ -22986,7 +22992,7 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="n">
+      <c r="S55" s="1" t="n">
         <v>0.04545454545454546</v>
       </c>
       <c r="T55" t="n">
@@ -23016,7 +23022,7 @@
       <c r="AB55" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AC55" s="1" t="n">
         <v>0.5681818181818182</v>
       </c>
       <c r="AD55" t="n">
@@ -23094,7 +23100,7 @@
       <c r="BB55" t="n">
         <v>0</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BC55" s="1" t="n">
         <v>0.1363636363636364</v>
       </c>
       <c r="BD55" t="n">
@@ -23103,7 +23109,7 @@
       <c r="BE55" t="n">
         <v>0</v>
       </c>
-      <c r="BF55" t="n">
+      <c r="BF55" s="1" t="n">
         <v>0.1136363636363636</v>
       </c>
       <c r="BG55" t="n">
@@ -23115,7 +23121,7 @@
       <c r="BI55" t="n">
         <v>0</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BJ55" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="BK55" t="n">
@@ -23172,7 +23178,7 @@
       <c r="CB55" t="n">
         <v>0</v>
       </c>
-      <c r="CC55" t="n">
+      <c r="CC55" s="1" t="n">
         <v>0.02272727272727273</v>
       </c>
       <c r="CD55" t="n">
@@ -23347,7 +23353,7 @@
           <t>NCCP000</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="1" t="n">
         <v>0.07142857142857142</v>
       </c>
       <c r="C56" t="n">
@@ -23359,7 +23365,7 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="1" t="n">
         <v>0.2142857142857143</v>
       </c>
       <c r="G56" t="n">
@@ -23401,7 +23407,7 @@
       <c r="S56" t="n">
         <v>0</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T56" s="1" t="n">
         <v>0.2142857142857143</v>
       </c>
       <c r="U56" t="n">
@@ -23431,10 +23437,10 @@
       <c r="AC56" t="n">
         <v>0</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AD56" s="1" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AE56" s="1" t="n">
         <v>0.07142857142857142</v>
       </c>
       <c r="AF56" t="n">
@@ -23449,7 +23455,7 @@
       <c r="AI56" t="n">
         <v>0</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AJ56" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AK56" t="n">
@@ -23494,7 +23500,7 @@
       <c r="AX56" t="n">
         <v>0</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="AY56" s="1" t="n">
         <v>0.07142857142857142</v>
       </c>
       <c r="AZ56" t="n">
@@ -23509,7 +23515,7 @@
       <c r="BC56" t="n">
         <v>0</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BD56" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="BE56" t="n">
@@ -23759,22 +23765,22 @@
           <t>VMIP3P0</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="1" t="n">
         <v>0.2926829268292683</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="H57" t="n">
@@ -23786,7 +23792,7 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="L57" t="n">
@@ -23810,10 +23816,10 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="n">
+      <c r="S57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="U57" t="n">
@@ -23822,10 +23828,10 @@
       <c r="V57" t="n">
         <v>0</v>
       </c>
-      <c r="W57" t="n">
+      <c r="W57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="X57" t="n">
+      <c r="X57" s="1" t="n">
         <v>0.1219512195121951</v>
       </c>
       <c r="Y57" t="n">
@@ -23840,10 +23846,10 @@
       <c r="AB57" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AC57" s="1" t="n">
         <v>0.07317073170731707</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AD57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="AE57" t="n">
@@ -23852,7 +23858,7 @@
       <c r="AF57" t="n">
         <v>0</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AG57" s="1" t="n">
         <v>0.1219512195121951</v>
       </c>
       <c r="AH57" t="n">
@@ -23861,7 +23867,7 @@
       <c r="AI57" t="n">
         <v>0</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AJ57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="AK57" t="n">
@@ -23879,13 +23885,13 @@
       <c r="AO57" t="n">
         <v>0</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AP57" s="1" t="n">
         <v>0.04878048780487805</v>
       </c>
       <c r="AQ57" t="n">
         <v>0</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AR57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="AS57" t="n">
@@ -23894,7 +23900,7 @@
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AU57" s="1" t="n">
         <v>0.04878048780487805</v>
       </c>
       <c r="AV57" t="n">
@@ -23936,10 +23942,10 @@
       <c r="BH57" t="n">
         <v>0</v>
       </c>
-      <c r="BI57" t="n">
+      <c r="BI57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="BJ57" t="n">
+      <c r="BJ57" s="1" t="n">
         <v>0.02439024390243903</v>
       </c>
       <c r="BK57" t="n">
@@ -24198,7 +24204,7 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="L58" t="n">
@@ -24225,7 +24231,7 @@
       <c r="S58" t="n">
         <v>0</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T58" s="1" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="U58" t="n">
@@ -24234,7 +24240,7 @@
       <c r="V58" t="n">
         <v>0</v>
       </c>
-      <c r="W58" t="n">
+      <c r="W58" s="1" t="n">
         <v>0.6363636363636364</v>
       </c>
       <c r="X58" t="n">
@@ -24339,7 +24345,7 @@
       <c r="BE58" t="n">
         <v>0</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BF58" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="BG58" t="n">
@@ -24583,10 +24589,10 @@
           <t>PR0CN000</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="1" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="1" t="n">
         <v>0.05128205128205128</v>
       </c>
       <c r="D59" t="n">
@@ -24595,10 +24601,10 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="1" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="H59" t="n">
@@ -24613,7 +24619,7 @@
       <c r="K59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59" s="1" t="n">
         <v>0.03846153846153846</v>
       </c>
       <c r="M59" t="n">
@@ -24628,7 +24634,7 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q59" s="1" t="n">
         <v>0.02564102564102564</v>
       </c>
       <c r="R59" t="n">
@@ -24640,7 +24646,7 @@
       <c r="T59" t="n">
         <v>0</v>
       </c>
-      <c r="U59" t="n">
+      <c r="U59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="V59" t="n">
@@ -24652,7 +24658,7 @@
       <c r="X59" t="n">
         <v>0</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Y59" s="1" t="n">
         <v>0.141025641025641</v>
       </c>
       <c r="Z59" t="n">
@@ -24667,7 +24673,7 @@
       <c r="AC59" t="n">
         <v>0</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AD59" s="1" t="n">
         <v>0.07692307692307693</v>
       </c>
       <c r="AE59" t="n">
@@ -24685,7 +24691,7 @@
       <c r="AI59" t="n">
         <v>0</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AJ59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="AK59" t="n">
@@ -24712,10 +24718,10 @@
       <c r="AR59" t="n">
         <v>0</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AS59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AT59" s="1" t="n">
         <v>0.1794871794871795</v>
       </c>
       <c r="AU59" t="n">
@@ -24730,7 +24736,7 @@
       <c r="AX59" t="n">
         <v>0</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="AY59" s="1" t="n">
         <v>0.1153846153846154</v>
       </c>
       <c r="AZ59" t="n">
@@ -24739,13 +24745,13 @@
       <c r="BA59" t="n">
         <v>0</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BB59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="BC59" t="n">
         <v>0</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BD59" s="1" t="n">
         <v>0.02564102564102564</v>
       </c>
       <c r="BE59" t="n">
@@ -24754,7 +24760,7 @@
       <c r="BF59" t="n">
         <v>0</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BG59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="BH59" t="n">
@@ -24775,7 +24781,7 @@
       <c r="BM59" t="n">
         <v>0</v>
       </c>
-      <c r="BN59" t="n">
+      <c r="BN59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="BO59" t="n">
@@ -24796,7 +24802,7 @@
       <c r="BT59" t="n">
         <v>0</v>
       </c>
-      <c r="BU59" t="n">
+      <c r="BU59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="BV59" t="n">
@@ -24805,7 +24811,7 @@
       <c r="BW59" t="n">
         <v>0</v>
       </c>
-      <c r="BX59" t="n">
+      <c r="BX59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="BY59" t="n">
@@ -24814,7 +24820,7 @@
       <c r="BZ59" t="n">
         <v>0</v>
       </c>
-      <c r="CA59" t="n">
+      <c r="CA59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="CB59" t="n">
@@ -24823,7 +24829,7 @@
       <c r="CC59" t="n">
         <v>0</v>
       </c>
-      <c r="CD59" t="n">
+      <c r="CD59" s="1" t="n">
         <v>0.03846153846153846</v>
       </c>
       <c r="CE59" t="n">
@@ -24835,7 +24841,7 @@
       <c r="CG59" t="n">
         <v>0</v>
       </c>
-      <c r="CH59" t="n">
+      <c r="CH59" s="1" t="n">
         <v>0.02564102564102564</v>
       </c>
       <c r="CI59" t="n">
@@ -24856,7 +24862,7 @@
       <c r="CN59" t="n">
         <v>0</v>
       </c>
-      <c r="CO59" t="n">
+      <c r="CO59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="CP59" t="n">
@@ -24874,7 +24880,7 @@
       <c r="CT59" t="n">
         <v>0</v>
       </c>
-      <c r="CU59" t="n">
+      <c r="CU59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="CV59" t="n">
@@ -24916,13 +24922,13 @@
       <c r="DH59" t="n">
         <v>0</v>
       </c>
-      <c r="DI59" t="n">
+      <c r="DI59" s="1" t="n">
         <v>0.01282051282051282</v>
       </c>
       <c r="DJ59" t="n">
         <v>0</v>
       </c>
-      <c r="DK59" t="n">
+      <c r="DK59" s="1" t="n">
         <v>0.05128205128205128</v>
       </c>
       <c r="DL59" t="n">
@@ -25007,7 +25013,7 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="G60" t="n">
@@ -25127,7 +25133,7 @@
       <c r="AS60" t="n">
         <v>0</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AT60" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="AU60" t="n">
@@ -25334,7 +25340,7 @@
       <c r="DJ60" t="n">
         <v>0</v>
       </c>
-      <c r="DK60" t="n">
+      <c r="DK60" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="DL60" t="n">
@@ -25416,7 +25422,7 @@
       <c r="D61" t="n">
         <v>0</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="F61" t="n">
@@ -25428,10 +25434,10 @@
       <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" s="1" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="K61" t="n">
@@ -25575,7 +25581,7 @@
       <c r="BE61" t="n">
         <v>0</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BF61" s="1" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="BG61" t="n">
@@ -25590,7 +25596,7 @@
       <c r="BJ61" t="n">
         <v>0</v>
       </c>
-      <c r="BK61" t="n">
+      <c r="BK61" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="BL61" t="n">
@@ -25828,10 +25834,10 @@
       <c r="D62" t="n">
         <v>0</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="1" t="n">
         <v>0.3</v>
       </c>
       <c r="G62" t="n">
@@ -25846,7 +25852,7 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K62" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="L62" t="n">
@@ -25882,7 +25888,7 @@
       <c r="V62" t="n">
         <v>0</v>
       </c>
-      <c r="W62" t="n">
+      <c r="W62" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="X62" t="n">
@@ -25900,7 +25906,7 @@
       <c r="AB62" t="n">
         <v>0</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AC62" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="AD62" t="n">
@@ -25921,7 +25927,7 @@
       <c r="AI62" t="n">
         <v>0</v>
       </c>
-      <c r="AJ62" t="n">
+      <c r="AJ62" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="AK62" t="n">
@@ -26243,7 +26249,7 @@
       <c r="E63" t="n">
         <v>0</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="G63" t="n">
@@ -26258,7 +26264,7 @@
       <c r="J63" t="n">
         <v>0</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="L63" t="n">
@@ -26285,7 +26291,7 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="n">
+      <c r="T63" s="1" t="n">
         <v>0.1333333333333333</v>
       </c>
       <c r="U63" t="n">
@@ -26312,7 +26318,7 @@
       <c r="AB63" t="n">
         <v>0</v>
       </c>
-      <c r="AC63" t="n">
+      <c r="AC63" s="1" t="n">
         <v>0.5333333333333333</v>
       </c>
       <c r="AD63" t="n">
@@ -26399,7 +26405,7 @@
       <c r="BE63" t="n">
         <v>0</v>
       </c>
-      <c r="BF63" t="n">
+      <c r="BF63" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="BG63" t="n">
@@ -26643,7 +26649,7 @@
           <t>PR0CS000</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="1" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="C64" t="n">
@@ -26658,7 +26664,7 @@
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="H64" t="n">
@@ -26682,7 +26688,7 @@
       <c r="N64" t="n">
         <v>0</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="P64" t="n">
@@ -26700,7 +26706,7 @@
       <c r="T64" t="n">
         <v>0</v>
       </c>
-      <c r="U64" t="n">
+      <c r="U64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="V64" t="n">
@@ -26727,7 +26733,7 @@
       <c r="AC64" t="n">
         <v>0</v>
       </c>
-      <c r="AD64" t="n">
+      <c r="AD64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="AE64" t="n">
@@ -26775,7 +26781,7 @@
       <c r="AS64" t="n">
         <v>0</v>
       </c>
-      <c r="AT64" t="n">
+      <c r="AT64" s="1" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="AU64" t="n">
@@ -26790,7 +26796,7 @@
       <c r="AX64" t="n">
         <v>0</v>
       </c>
-      <c r="AY64" t="n">
+      <c r="AY64" s="1" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="AZ64" t="n">
@@ -26883,10 +26889,10 @@
       <c r="CC64" t="n">
         <v>0</v>
       </c>
-      <c r="CD64" t="n">
+      <c r="CD64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="CE64" t="n">
+      <c r="CE64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="CF64" t="n">
@@ -26907,7 +26913,7 @@
       <c r="CK64" t="n">
         <v>0</v>
       </c>
-      <c r="CL64" t="n">
+      <c r="CL64" s="1" t="n">
         <v>0.05882352941176471</v>
       </c>
       <c r="CM64" t="n">
@@ -26982,10 +26988,10 @@
       <c r="DJ64" t="n">
         <v>0</v>
       </c>
-      <c r="DK64" t="n">
+      <c r="DK64" s="1" t="n">
         <v>0.1176470588235294</v>
       </c>
-      <c r="DL64" t="n">
+      <c r="DL64" s="1" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="DM64" t="n">
@@ -27136,7 +27142,7 @@
       <c r="AB65" t="n">
         <v>0</v>
       </c>
-      <c r="AC65" t="n">
+      <c r="AC65" s="1" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="AD65" t="n">
@@ -27214,7 +27220,7 @@
       <c r="BB65" t="n">
         <v>0</v>
       </c>
-      <c r="BC65" t="n">
+      <c r="BC65" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="BD65" t="n">
@@ -27241,10 +27247,10 @@
       <c r="BK65" t="n">
         <v>0</v>
       </c>
-      <c r="BL65" t="n">
+      <c r="BL65" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="BM65" t="n">
+      <c r="BM65" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="BN65" t="n">
@@ -27442,7 +27448,7 @@
       <c r="DZ65" t="n">
         <v>0</v>
       </c>
-      <c r="EA65" t="n">
+      <c r="EA65" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="EB65" t="n">
@@ -27467,25 +27473,25 @@
           <t>Fe</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="1" t="n">
         <v>0.1481481481481481</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="1" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="1" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="I66" t="n">
@@ -27494,7 +27500,7 @@
       <c r="J66" t="n">
         <v>0</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K66" s="1" t="n">
         <v>0.1296296296296296</v>
       </c>
       <c r="L66" t="n">
@@ -27503,13 +27509,13 @@
       <c r="M66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="P66" t="n">
+      <c r="P66" s="1" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="Q66" t="n">
@@ -27518,7 +27524,7 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="n">
+      <c r="S66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="T66" t="n">
@@ -27527,7 +27533,7 @@
       <c r="U66" t="n">
         <v>0</v>
       </c>
-      <c r="V66" t="n">
+      <c r="V66" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="W66" t="n">
@@ -27548,10 +27554,10 @@
       <c r="AB66" t="n">
         <v>0</v>
       </c>
-      <c r="AC66" t="n">
+      <c r="AC66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="AD66" t="n">
+      <c r="AD66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="AE66" t="n">
@@ -27569,7 +27575,7 @@
       <c r="AI66" t="n">
         <v>0</v>
       </c>
-      <c r="AJ66" t="n">
+      <c r="AJ66" s="1" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="AK66" t="n">
@@ -27587,7 +27593,7 @@
       <c r="AO66" t="n">
         <v>0</v>
       </c>
-      <c r="AP66" t="n">
+      <c r="AP66" s="1" t="n">
         <v>0.03703703703703703</v>
       </c>
       <c r="AQ66" t="n">
@@ -27599,7 +27605,7 @@
       <c r="AS66" t="n">
         <v>0</v>
       </c>
-      <c r="AT66" t="n">
+      <c r="AT66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="AU66" t="n">
@@ -27635,7 +27641,7 @@
       <c r="BE66" t="n">
         <v>0</v>
       </c>
-      <c r="BF66" t="n">
+      <c r="BF66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="BG66" t="n">
@@ -27659,16 +27665,16 @@
       <c r="BM66" t="n">
         <v>0</v>
       </c>
-      <c r="BN66" t="n">
+      <c r="BN66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="BO66" t="n">
         <v>0</v>
       </c>
-      <c r="BP66" t="n">
+      <c r="BP66" s="1" t="n">
         <v>0.09259259259259259</v>
       </c>
-      <c r="BQ66" t="n">
+      <c r="BQ66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="BR66" t="n">
@@ -27683,7 +27689,7 @@
       <c r="BU66" t="n">
         <v>0</v>
       </c>
-      <c r="BV66" t="n">
+      <c r="BV66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="BW66" t="n">
@@ -27779,7 +27785,7 @@
       <c r="DA66" t="n">
         <v>0</v>
       </c>
-      <c r="DB66" t="n">
+      <c r="DB66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="DC66" t="n">
@@ -27821,7 +27827,7 @@
       <c r="DO66" t="n">
         <v>0</v>
       </c>
-      <c r="DP66" t="n">
+      <c r="DP66" s="1" t="n">
         <v>0.01851851851851852</v>
       </c>
       <c r="DQ66" t="n">
@@ -27885,10 +27891,10 @@
       <c r="C67" t="n">
         <v>0</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="F67" t="n">
@@ -27906,7 +27912,7 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="L67" t="n">
@@ -27915,7 +27921,7 @@
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N67" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="O67" t="n">
@@ -28303,13 +28309,13 @@
       <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="1" t="n">
         <v>0.625</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="I68" t="n">
@@ -28345,7 +28351,7 @@
       <c r="S68" t="n">
         <v>0</v>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="U68" t="n">
@@ -28357,7 +28363,7 @@
       <c r="W68" t="n">
         <v>0</v>
       </c>
-      <c r="X68" t="n">
+      <c r="X68" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="Y68" t="n">
@@ -28703,7 +28709,7 @@
           <t>Fpa</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="1" t="n">
         <v>0.3870967741935484</v>
       </c>
       <c r="C69" t="n">
@@ -28712,16 +28718,16 @@
       <c r="D69" t="n">
         <v>0</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="1" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="1" t="n">
         <v>0.1935483870967742</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="1" t="n">
         <v>0.1290322580645161</v>
       </c>
       <c r="I69" t="n">
@@ -28754,7 +28760,7 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="n">
+      <c r="S69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="T69" t="n">
@@ -28769,7 +28775,7 @@
       <c r="W69" t="n">
         <v>0</v>
       </c>
-      <c r="X69" t="n">
+      <c r="X69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="Y69" t="n">
@@ -28823,13 +28829,13 @@
       <c r="AO69" t="n">
         <v>0</v>
       </c>
-      <c r="AP69" t="n">
+      <c r="AP69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="AQ69" t="n">
         <v>0</v>
       </c>
-      <c r="AR69" t="n">
+      <c r="AR69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="AS69" t="n">
@@ -28892,7 +28898,7 @@
       <c r="BL69" t="n">
         <v>0</v>
       </c>
-      <c r="BM69" t="n">
+      <c r="BM69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="BN69" t="n">
@@ -28964,7 +28970,7 @@
       <c r="CJ69" t="n">
         <v>0</v>
       </c>
-      <c r="CK69" t="n">
+      <c r="CK69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="CL69" t="n">
@@ -29015,7 +29021,7 @@
       <c r="DA69" t="n">
         <v>0</v>
       </c>
-      <c r="DB69" t="n">
+      <c r="DB69" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="DC69" t="n">
@@ -29118,7 +29124,7 @@
       <c r="B70" t="n">
         <v>0</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="D70" t="n">
@@ -29127,7 +29133,7 @@
       <c r="E70" t="n">
         <v>0</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="1" t="n">
         <v>0.06451612903225806</v>
       </c>
       <c r="G70" t="n">
@@ -29142,7 +29148,7 @@
       <c r="J70" t="n">
         <v>0</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K70" s="1" t="n">
         <v>0.1612903225806452</v>
       </c>
       <c r="L70" t="n">
@@ -29154,7 +29160,7 @@
       <c r="N70" t="n">
         <v>0</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="P70" t="n">
@@ -29169,7 +29175,7 @@
       <c r="S70" t="n">
         <v>0</v>
       </c>
-      <c r="T70" t="n">
+      <c r="T70" s="1" t="n">
         <v>0.06451612903225806</v>
       </c>
       <c r="U70" t="n">
@@ -29181,7 +29187,7 @@
       <c r="W70" t="n">
         <v>0</v>
       </c>
-      <c r="X70" t="n">
+      <c r="X70" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="Y70" t="n">
@@ -29217,7 +29223,7 @@
       <c r="AI70" t="n">
         <v>0</v>
       </c>
-      <c r="AJ70" t="n">
+      <c r="AJ70" s="1" t="n">
         <v>0.2580645161290323</v>
       </c>
       <c r="AK70" t="n">
@@ -29247,7 +29253,7 @@
       <c r="AS70" t="n">
         <v>0</v>
       </c>
-      <c r="AT70" t="n">
+      <c r="AT70" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="AU70" t="n">
@@ -29331,7 +29337,7 @@
       <c r="BU70" t="n">
         <v>0</v>
       </c>
-      <c r="BV70" t="n">
+      <c r="BV70" s="1" t="n">
         <v>0.2580645161290323</v>
       </c>
       <c r="BW70" t="n">
@@ -29355,7 +29361,7 @@
       <c r="CC70" t="n">
         <v>0</v>
       </c>
-      <c r="CD70" t="n">
+      <c r="CD70" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="CE70" t="n">
@@ -29424,7 +29430,7 @@
       <c r="CZ70" t="n">
         <v>0</v>
       </c>
-      <c r="DA70" t="n">
+      <c r="DA70" s="1" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="DB70" t="n">
@@ -29539,7 +29545,7 @@
       <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="G71" t="n">
@@ -29578,7 +29584,7 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="n">
+      <c r="S71" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="T71" t="n">
@@ -29587,7 +29593,7 @@
       <c r="U71" t="n">
         <v>0</v>
       </c>
-      <c r="V71" t="n">
+      <c r="V71" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="W71" t="n">
@@ -29653,7 +29659,7 @@
       <c r="AQ71" t="n">
         <v>0</v>
       </c>
-      <c r="AR71" t="n">
+      <c r="AR71" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AS71" t="n">
@@ -29951,7 +29957,7 @@
       <c r="E72" t="n">
         <v>0</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
@@ -30387,7 +30393,7 @@
       <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N73" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="O73" t="n">
@@ -30435,7 +30441,7 @@
       <c r="AC73" t="n">
         <v>0</v>
       </c>
-      <c r="AD73" t="n">
+      <c r="AD73" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AE73" t="n">
@@ -30483,7 +30489,7 @@
       <c r="AS73" t="n">
         <v>0</v>
       </c>
-      <c r="AT73" t="n">
+      <c r="AT73" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AU73" t="n">
@@ -30555,7 +30561,7 @@
       <c r="BQ73" t="n">
         <v>0</v>
       </c>
-      <c r="BR73" t="n">
+      <c r="BR73" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="BS73" t="n">
@@ -30775,7 +30781,7 @@
       <c r="E74" t="n">
         <v>0</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="G74" t="n">
@@ -30835,7 +30841,7 @@
       <c r="Y74" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" t="n">
+      <c r="Z74" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AA74" t="n">
@@ -30844,7 +30850,7 @@
       <c r="AB74" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" t="n">
+      <c r="AC74" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AD74" t="n">
@@ -30880,7 +30886,7 @@
       <c r="AN74" t="n">
         <v>0</v>
       </c>
-      <c r="AO74" t="n">
+      <c r="AO74" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AP74" t="n">
@@ -31175,7 +31181,7 @@
           <t>Fx</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="1" t="n">
         <v>0.72</v>
       </c>
       <c r="C75" t="n">
@@ -31187,7 +31193,7 @@
       <c r="E75" t="n">
         <v>0</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="1" t="n">
         <v>0.12</v>
       </c>
       <c r="G75" t="n">
@@ -31229,7 +31235,7 @@
       <c r="S75" t="n">
         <v>0</v>
       </c>
-      <c r="T75" t="n">
+      <c r="T75" s="1" t="n">
         <v>0.08</v>
       </c>
       <c r="U75" t="n">
@@ -31310,7 +31316,7 @@
       <c r="AT75" t="n">
         <v>0</v>
       </c>
-      <c r="AU75" t="n">
+      <c r="AU75" s="1" t="n">
         <v>0.04</v>
       </c>
       <c r="AV75" t="n">
@@ -31394,7 +31400,7 @@
       <c r="BV75" t="n">
         <v>0</v>
       </c>
-      <c r="BW75" t="n">
+      <c r="BW75" s="1" t="n">
         <v>0.04</v>
       </c>
       <c r="BX75" t="n">
@@ -31809,7 +31815,7 @@
       <c r="BW76" t="n">
         <v>0</v>
       </c>
-      <c r="BX76" t="n">
+      <c r="BX76" s="1" t="n">
         <v>1</v>
       </c>
       <c r="BY76" t="n">
@@ -32014,7 +32020,7 @@
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="H77" t="n">
@@ -32080,7 +32086,7 @@
       <c r="AB77" t="n">
         <v>0</v>
       </c>
-      <c r="AC77" t="n">
+      <c r="AC77" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="AD77" t="n">
@@ -32429,7 +32435,7 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="n">
@@ -32832,7 +32838,7 @@
       <c r="D79" t="n">
         <v>0</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="F79" t="n">
@@ -32847,7 +32853,7 @@
       <c r="I79" t="n">
         <v>0</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K79" t="n">
@@ -33247,7 +33253,7 @@
       <c r="E80" t="n">
         <v>0</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="G80" t="n">
@@ -33367,7 +33373,7 @@
       <c r="AS80" t="n">
         <v>0</v>
       </c>
-      <c r="AT80" t="n">
+      <c r="AT80" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="AU80" t="n">
@@ -33403,7 +33409,7 @@
       <c r="BE80" t="n">
         <v>0</v>
       </c>
-      <c r="BF80" t="n">
+      <c r="BF80" s="1" t="n">
         <v>0.4</v>
       </c>
       <c r="BG80" t="n">
@@ -33574,7 +33580,7 @@
       <c r="DJ80" t="n">
         <v>0</v>
       </c>
-      <c r="DK80" t="n">
+      <c r="DK80" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="DL80" t="n">
@@ -33647,7 +33653,7 @@
           <t>NCCS000</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="C81" t="n">
@@ -33659,7 +33665,7 @@
       <c r="E81" t="n">
         <v>0</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="G81" t="n">
@@ -33674,7 +33680,7 @@
       <c r="J81" t="n">
         <v>0</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="L81" t="n">
@@ -33716,7 +33722,7 @@
       <c r="X81" t="n">
         <v>0</v>
       </c>
-      <c r="Y81" t="n">
+      <c r="Y81" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="Z81" t="n">
@@ -33731,7 +33737,7 @@
       <c r="AC81" t="n">
         <v>0</v>
       </c>
-      <c r="AD81" t="n">
+      <c r="AD81" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AE81" t="n">
@@ -33749,7 +33755,7 @@
       <c r="AI81" t="n">
         <v>0</v>
       </c>
-      <c r="AJ81" t="n">
+      <c r="AJ81" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AK81" t="n">
@@ -33830,7 +33836,7 @@
       <c r="BJ81" t="n">
         <v>0</v>
       </c>
-      <c r="BK81" t="n">
+      <c r="BK81" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="BL81" t="n">
@@ -34191,7 +34197,7 @@
       <c r="AS82" t="n">
         <v>0</v>
       </c>
-      <c r="AT82" t="n">
+      <c r="AT82" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="AU82" t="n">
@@ -34332,7 +34338,7 @@
       <c r="CN82" t="n">
         <v>0</v>
       </c>
-      <c r="CO82" t="n">
+      <c r="CO82" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="CP82" t="n">
@@ -34483,7 +34489,7 @@
       <c r="E83" t="n">
         <v>0</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="G83" t="n">
@@ -34540,7 +34546,7 @@
       <c r="X83" t="n">
         <v>0</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="Y83" s="1" t="n">
         <v>0.1363636363636364</v>
       </c>
       <c r="Z83" t="n">
@@ -34603,7 +34609,7 @@
       <c r="AS83" t="n">
         <v>0</v>
       </c>
-      <c r="AT83" t="n">
+      <c r="AT83" s="1" t="n">
         <v>0.4090909090909091</v>
       </c>
       <c r="AU83" t="n">
@@ -34633,7 +34639,7 @@
       <c r="BC83" t="n">
         <v>0</v>
       </c>
-      <c r="BD83" t="n">
+      <c r="BD83" s="1" t="n">
         <v>0.1363636363636364</v>
       </c>
       <c r="BE83" t="n">
@@ -34729,7 +34735,7 @@
       <c r="CI83" t="n">
         <v>0</v>
       </c>
-      <c r="CJ83" t="n">
+      <c r="CJ83" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="CK83" t="n">
@@ -34810,10 +34816,10 @@
       <c r="DJ83" t="n">
         <v>0</v>
       </c>
-      <c r="DK83" t="n">
+      <c r="DK83" s="1" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="DL83" t="n">
+      <c r="DL83" s="1" t="n">
         <v>0.04545454545454546</v>
       </c>
       <c r="DM83" t="n">
@@ -34895,7 +34901,7 @@
       <c r="E84" t="n">
         <v>0</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="G84" t="n">
@@ -34955,7 +34961,7 @@
       <c r="Y84" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" t="n">
+      <c r="Z84" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AA84" t="n">
@@ -35009,7 +35015,7 @@
       <c r="AQ84" t="n">
         <v>0</v>
       </c>
-      <c r="AR84" t="n">
+      <c r="AR84" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="AS84" t="n">
@@ -35072,7 +35078,7 @@
       <c r="BL84" t="n">
         <v>0</v>
       </c>
-      <c r="BM84" t="n">
+      <c r="BM84" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="BN84" t="n">
@@ -35316,7 +35322,7 @@
       <c r="H85" t="n">
         <v>0</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="J85" t="n">
@@ -35544,7 +35550,7 @@
       <c r="CF85" t="n">
         <v>0</v>
       </c>
-      <c r="CG85" t="n">
+      <c r="CG85" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="CH85" t="n">
@@ -35722,7 +35728,7 @@
       <c r="F86" t="n">
         <v>0</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
@@ -35740,7 +35746,7 @@
       <c r="L86" t="n">
         <v>0</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="N86" t="n">
@@ -36131,7 +36137,7 @@
       <c r="E87" t="n">
         <v>0</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G87" t="n">
@@ -36239,7 +36245,7 @@
       <c r="AO87" t="n">
         <v>0</v>
       </c>
-      <c r="AP87" t="n">
+      <c r="AP87" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ87" t="n">
@@ -36543,7 +36549,7 @@
       <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="1" t="n">
         <v>0.75</v>
       </c>
       <c r="G88" t="n">
@@ -36585,7 +36591,7 @@
       <c r="S88" t="n">
         <v>0</v>
       </c>
-      <c r="T88" t="n">
+      <c r="T88" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="U88" t="n">
@@ -36979,13 +36985,13 @@
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="P89" t="n">
+      <c r="P89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q89" t="n">
@@ -37045,7 +37051,7 @@
       <c r="AI89" t="n">
         <v>0</v>
       </c>
-      <c r="AJ89" t="n">
+      <c r="AJ89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AK89" t="n">
@@ -37063,13 +37069,13 @@
       <c r="AO89" t="n">
         <v>0</v>
       </c>
-      <c r="AP89" t="n">
+      <c r="AP89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AQ89" t="n">
         <v>0</v>
       </c>
-      <c r="AR89" t="n">
+      <c r="AR89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AS89" t="n">
@@ -37183,7 +37189,7 @@
       <c r="CC89" t="n">
         <v>0</v>
       </c>
-      <c r="CD89" t="n">
+      <c r="CD89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="CE89" t="n">
@@ -37306,7 +37312,7 @@
       <c r="DR89" t="n">
         <v>0</v>
       </c>
-      <c r="DS89" t="n">
+      <c r="DS89" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="DT89" t="n">
@@ -37355,10 +37361,10 @@
           <t>PD0NS000</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="D90" t="n">
@@ -37439,7 +37445,7 @@
       <c r="AC90" t="n">
         <v>0</v>
       </c>
-      <c r="AD90" t="n">
+      <c r="AD90" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AE90" t="n">
@@ -37457,7 +37463,7 @@
       <c r="AI90" t="n">
         <v>0</v>
       </c>
-      <c r="AJ90" t="n">
+      <c r="AJ90" s="1" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="AK90" t="n">
@@ -37487,7 +37493,7 @@
       <c r="AS90" t="n">
         <v>0</v>
       </c>
-      <c r="AT90" t="n">
+      <c r="AT90" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AU90" t="n">
@@ -37502,7 +37508,7 @@
       <c r="AX90" t="n">
         <v>0</v>
       </c>
-      <c r="AY90" t="n">
+      <c r="AY90" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="AZ90" t="n">
@@ -37767,7 +37773,7 @@
           <t>DI0CS0</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="C91" t="n">
@@ -37776,7 +37782,7 @@
       <c r="D91" t="n">
         <v>0</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="1" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="F91" t="n">
@@ -37785,7 +37791,7 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" s="1" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="I91" t="n">
@@ -38188,7 +38194,7 @@
       <c r="D92" t="n">
         <v>0</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="1" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="F92" t="n">
@@ -38218,7 +38224,7 @@
       <c r="N92" t="n">
         <v>0</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92" s="1" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="P92" t="n">
@@ -38603,7 +38609,7 @@
       <c r="E93" t="n">
         <v>0</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
@@ -39027,7 +39033,7 @@
       <c r="I94" t="n">
         <v>0</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="K94" t="n">
@@ -39090,7 +39096,7 @@
       <c r="AD94" t="n">
         <v>0</v>
       </c>
-      <c r="AE94" t="n">
+      <c r="AE94" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AF94" t="n">
@@ -39138,7 +39144,7 @@
       <c r="AT94" t="n">
         <v>0</v>
       </c>
-      <c r="AU94" t="n">
+      <c r="AU94" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AV94" t="n">
@@ -39418,7 +39424,7 @@
       <c r="B95" t="n">
         <v>0</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="D95" t="n">
@@ -39442,10 +39448,10 @@
       <c r="J95" t="n">
         <v>0</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="M95" t="n">
@@ -39547,7 +39553,7 @@
       <c r="AS95" t="n">
         <v>0</v>
       </c>
-      <c r="AT95" t="n">
+      <c r="AT95" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="AU95" t="n">
@@ -39754,7 +39760,7 @@
       <c r="DJ95" t="n">
         <v>0</v>
       </c>
-      <c r="DK95" t="n">
+      <c r="DK95" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="DL95" t="n">
@@ -39851,7 +39857,7 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K96" t="n">
@@ -40248,7 +40254,7 @@
       <c r="D97" t="n">
         <v>0</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="F97" t="n">
@@ -40257,7 +40263,7 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="I97" t="n">
@@ -40783,7 +40789,7 @@
       <c r="AS98" t="n">
         <v>0</v>
       </c>
-      <c r="AT98" t="n">
+      <c r="AT98" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU98" t="n">
@@ -41075,7 +41081,7 @@
       <c r="E99" t="n">
         <v>0</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
@@ -41496,7 +41502,7 @@
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J100" t="n">
@@ -42019,7 +42025,7 @@
       <c r="AS101" t="n">
         <v>0</v>
       </c>
-      <c r="AT101" t="n">
+      <c r="AT101" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU101" t="n">
@@ -42323,7 +42329,7 @@
       <c r="I102" t="n">
         <v>0</v>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K102" t="n">
@@ -42804,7 +42810,7 @@
       <c r="AF103" t="n">
         <v>0</v>
       </c>
-      <c r="AG103" t="n">
+      <c r="AG103" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AH103" t="n">
@@ -43429,7 +43435,7 @@
       <c r="CY104" t="n">
         <v>0</v>
       </c>
-      <c r="CZ104" t="n">
+      <c r="CZ104" s="1" t="n">
         <v>1</v>
       </c>
       <c r="DA104" t="n">
@@ -43637,7 +43643,7 @@
       <c r="AI105" t="n">
         <v>0</v>
       </c>
-      <c r="AJ105" t="n">
+      <c r="AJ105" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AK105" t="n">
@@ -44031,7 +44037,7 @@
       <c r="AC106" t="n">
         <v>0</v>
       </c>
-      <c r="AD106" t="n">
+      <c r="AD106" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="AE106" t="n">
@@ -44136,7 +44142,7 @@
       <c r="BL106" t="n">
         <v>0</v>
       </c>
-      <c r="BM106" t="n">
+      <c r="BM106" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="BN106" t="n">
@@ -44145,7 +44151,7 @@
       <c r="BO106" t="n">
         <v>0</v>
       </c>
-      <c r="BP106" t="n">
+      <c r="BP106" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="BQ106" t="n">
@@ -44368,10 +44374,10 @@
       <c r="D107" t="n">
         <v>0</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G107" t="n">
@@ -44395,7 +44401,7 @@
       <c r="M107" t="n">
         <v>0</v>
       </c>
-      <c r="N107" t="n">
+      <c r="N107" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="O107" t="n">
@@ -44771,7 +44777,7 @@
           <t>VAIS3S0</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="C108" t="n">
@@ -44795,7 +44801,7 @@
       <c r="I108" t="n">
         <v>0</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J108" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K108" t="n">
@@ -45183,7 +45189,7 @@
           <t>VMSP2S0</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C109" t="n">
@@ -45607,7 +45613,7 @@
       <c r="E110" t="n">
         <v>0</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
@@ -46007,7 +46013,7 @@
           <t>NC00000</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C111" t="n">
@@ -46431,7 +46437,7 @@
       <c r="E112" t="n">
         <v>0</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G112" t="n">
@@ -46473,7 +46479,7 @@
       <c r="S112" t="n">
         <v>0</v>
       </c>
-      <c r="T112" t="n">
+      <c r="T112" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="U112" t="n">
@@ -46918,7 +46924,7 @@
       <c r="AD113" t="n">
         <v>0</v>
       </c>
-      <c r="AE113" t="n">
+      <c r="AE113" s="1" t="n">
         <v>0.4</v>
       </c>
       <c r="AF113" t="n">
@@ -46987,7 +46993,7 @@
       <c r="BA113" t="n">
         <v>0</v>
       </c>
-      <c r="BB113" t="n">
+      <c r="BB113" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="BC113" t="n">
@@ -47086,7 +47092,7 @@
       <c r="CH113" t="n">
         <v>0</v>
       </c>
-      <c r="CI113" t="n">
+      <c r="CI113" s="1" t="n">
         <v>0.4</v>
       </c>
       <c r="CJ113" t="n">
@@ -47255,7 +47261,7 @@
       <c r="E114" t="n">
         <v>0</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="G114" t="n">
@@ -47264,7 +47270,7 @@
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="J114" t="n">
@@ -47288,7 +47294,7 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="Q114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="R114" t="n">
@@ -47297,7 +47303,7 @@
       <c r="S114" t="n">
         <v>0</v>
       </c>
-      <c r="T114" t="n">
+      <c r="T114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="U114" t="n">
@@ -47345,7 +47351,7 @@
       <c r="AI114" t="n">
         <v>0</v>
       </c>
-      <c r="AJ114" t="n">
+      <c r="AJ114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AK114" t="n">
@@ -47390,7 +47396,7 @@
       <c r="AX114" t="n">
         <v>0</v>
       </c>
-      <c r="AY114" t="n">
+      <c r="AY114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="AZ114" t="n">
@@ -47483,7 +47489,7 @@
       <c r="CC114" t="n">
         <v>0</v>
       </c>
-      <c r="CD114" t="n">
+      <c r="CD114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="CE114" t="n">
@@ -47582,10 +47588,10 @@
       <c r="DJ114" t="n">
         <v>0</v>
       </c>
-      <c r="DK114" t="n">
+      <c r="DK114" s="1" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="DL114" t="n">
+      <c r="DL114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="DM114" t="n">
@@ -47624,7 +47630,7 @@
       <c r="DX114" t="n">
         <v>0</v>
       </c>
-      <c r="DY114" t="n">
+      <c r="DY114" s="1" t="n">
         <v>0.08333333333333333</v>
       </c>
       <c r="DZ114" t="n">
@@ -47667,7 +47673,7 @@
       <c r="E115" t="n">
         <v>0</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="G115" t="n">
@@ -47682,7 +47688,7 @@
       <c r="J115" t="n">
         <v>0</v>
       </c>
-      <c r="K115" t="n">
+      <c r="K115" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="L115" t="n">
@@ -47802,7 +47808,7 @@
       <c r="AX115" t="n">
         <v>0</v>
       </c>
-      <c r="AY115" t="n">
+      <c r="AY115" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="AZ115" t="n">
@@ -47817,7 +47823,7 @@
       <c r="BC115" t="n">
         <v>0</v>
       </c>
-      <c r="BD115" t="n">
+      <c r="BD115" s="1" t="n">
         <v>0.4</v>
       </c>
       <c r="BE115" t="n">
@@ -48067,7 +48073,7 @@
           <t>VMII1S0</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="C116" t="n">
@@ -48079,10 +48085,10 @@
       <c r="E116" t="n">
         <v>0</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="H116" t="n">
@@ -48094,7 +48100,7 @@
       <c r="J116" t="n">
         <v>0</v>
       </c>
-      <c r="K116" t="n">
+      <c r="K116" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="L116" t="n">
@@ -48103,7 +48109,7 @@
       <c r="M116" t="n">
         <v>0</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="O116" t="n">
@@ -48118,7 +48124,7 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S116" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="T116" t="n">
@@ -48127,19 +48133,19 @@
       <c r="U116" t="n">
         <v>0</v>
       </c>
-      <c r="V116" t="n">
+      <c r="V116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="W116" t="n">
         <v>0</v>
       </c>
-      <c r="X116" t="n">
+      <c r="X116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="Y116" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" t="n">
+      <c r="Z116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="AA116" t="n">
@@ -48160,7 +48166,7 @@
       <c r="AF116" t="n">
         <v>0</v>
       </c>
-      <c r="AG116" t="n">
+      <c r="AG116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="AH116" t="n">
@@ -48169,7 +48175,7 @@
       <c r="AI116" t="n">
         <v>0</v>
       </c>
-      <c r="AJ116" t="n">
+      <c r="AJ116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="AK116" t="n">
@@ -48187,13 +48193,13 @@
       <c r="AO116" t="n">
         <v>0</v>
       </c>
-      <c r="AP116" t="n">
+      <c r="AP116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="AQ116" t="n">
         <v>0</v>
       </c>
-      <c r="AR116" t="n">
+      <c r="AR116" s="1" t="n">
         <v>0.06666666666666667</v>
       </c>
       <c r="AS116" t="n">
@@ -48253,7 +48259,7 @@
       <c r="BK116" t="n">
         <v>0</v>
       </c>
-      <c r="BL116" t="n">
+      <c r="BL116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="BM116" t="n">
@@ -48268,7 +48274,7 @@
       <c r="BP116" t="n">
         <v>0</v>
       </c>
-      <c r="BQ116" t="n">
+      <c r="BQ116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="BR116" t="n">
@@ -48298,7 +48304,7 @@
       <c r="BZ116" t="n">
         <v>0</v>
       </c>
-      <c r="CA116" t="n">
+      <c r="CA116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="CB116" t="n">
@@ -48403,7 +48409,7 @@
       <c r="DI116" t="n">
         <v>0</v>
       </c>
-      <c r="DJ116" t="n">
+      <c r="DJ116" s="1" t="n">
         <v>0.03333333333333333</v>
       </c>
       <c r="DK116" t="n">
@@ -48491,7 +48497,7 @@
       <c r="E117" t="n">
         <v>0</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="G117" t="n">
@@ -48503,7 +48509,7 @@
       <c r="I117" t="n">
         <v>0</v>
       </c>
-      <c r="J117" t="n">
+      <c r="J117" s="1" t="n">
         <v>0.6875</v>
       </c>
       <c r="K117" t="n">
@@ -48563,7 +48569,7 @@
       <c r="AC117" t="n">
         <v>0</v>
       </c>
-      <c r="AD117" t="n">
+      <c r="AD117" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="AE117" t="n">
@@ -48590,7 +48596,7 @@
       <c r="AL117" t="n">
         <v>0</v>
       </c>
-      <c r="AM117" t="n">
+      <c r="AM117" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="AN117" t="n">
@@ -48668,7 +48674,7 @@
       <c r="BL117" t="n">
         <v>0</v>
       </c>
-      <c r="BM117" t="n">
+      <c r="BM117" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="BN117" t="n">
@@ -48728,7 +48734,7 @@
       <c r="CF117" t="n">
         <v>0</v>
       </c>
-      <c r="CG117" t="n">
+      <c r="CG117" s="1" t="n">
         <v>0.0625</v>
       </c>
       <c r="CH117" t="n">
@@ -49023,7 +49029,7 @@
       <c r="AS118" t="n">
         <v>0</v>
       </c>
-      <c r="AT118" t="n">
+      <c r="AT118" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AU118" t="n">
@@ -49321,7 +49327,7 @@
       <c r="G119" t="n">
         <v>0</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H119" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I119" t="n">
@@ -49727,7 +49733,7 @@
       <c r="E120" t="n">
         <v>0</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G120" t="n">
@@ -50133,7 +50139,7 @@
       <c r="C121" t="n">
         <v>0</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="E121" t="n">
@@ -50148,7 +50154,7 @@
       <c r="H121" t="n">
         <v>0</v>
       </c>
-      <c r="I121" t="n">
+      <c r="I121" s="1" t="n">
         <v>0.4</v>
       </c>
       <c r="J121" t="n">
@@ -50211,7 +50217,7 @@
       <c r="AC121" t="n">
         <v>0</v>
       </c>
-      <c r="AD121" t="n">
+      <c r="AD121" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="AE121" t="n">
@@ -50220,7 +50226,7 @@
       <c r="AF121" t="n">
         <v>0</v>
       </c>
-      <c r="AG121" t="n">
+      <c r="AG121" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="AH121" t="n">
@@ -50608,7 +50614,7 @@
       <c r="X122" t="n">
         <v>0</v>
       </c>
-      <c r="Y122" t="n">
+      <c r="Y122" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z122" t="n">
@@ -50993,7 +50999,7 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="P123" t="n">
+      <c r="P123" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q123" t="n">
@@ -51435,7 +51441,7 @@
       <c r="Y124" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" t="n">
+      <c r="Z124" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA124" t="n">
@@ -51859,7 +51865,7 @@
       <c r="AC125" t="n">
         <v>0</v>
       </c>
-      <c r="AD125" t="n">
+      <c r="AD125" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE125" t="n">
@@ -52256,7 +52262,7 @@
       <c r="X126" t="n">
         <v>0</v>
       </c>
-      <c r="Y126" t="n">
+      <c r="Y126" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z126" t="n">
@@ -52611,7 +52617,7 @@
       <c r="E127" t="n">
         <v>0</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="G127" t="n">
@@ -52749,7 +52755,7 @@
       <c r="AY127" t="n">
         <v>0</v>
       </c>
-      <c r="AZ127" t="n">
+      <c r="AZ127" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="BA127" t="n">
@@ -53092,7 +53098,7 @@
       <c r="AB128" t="n">
         <v>0</v>
       </c>
-      <c r="AC128" t="n">
+      <c r="AC128" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AD128" t="n">
@@ -53432,7 +53438,7 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="F129" t="n">
@@ -53486,7 +53492,7 @@
       <c r="V129" t="n">
         <v>0</v>
       </c>
-      <c r="W129" t="n">
+      <c r="W129" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="X129" t="n">
@@ -53919,7 +53925,7 @@
       <c r="AC130" t="n">
         <v>0</v>
       </c>
-      <c r="AD130" t="n">
+      <c r="AD130" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE130" t="n">
@@ -54313,7 +54319,7 @@
       <c r="W131" t="n">
         <v>0</v>
       </c>
-      <c r="X131" t="n">
+      <c r="X131" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Y131" t="n">
@@ -54722,7 +54728,7 @@
       <c r="V132" t="n">
         <v>0</v>
       </c>
-      <c r="W132" t="n">
+      <c r="W132" s="1" t="n">
         <v>1</v>
       </c>
       <c r="X132" t="n">
@@ -55140,7 +55146,7 @@
       <c r="X133" t="n">
         <v>0</v>
       </c>
-      <c r="Y133" t="n">
+      <c r="Y133" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z133" t="n">
@@ -55495,7 +55501,7 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G134" t="n">
@@ -56237,7 +56243,7 @@
       <c r="DK135" t="n">
         <v>0</v>
       </c>
-      <c r="DL135" t="n">
+      <c r="DL135" s="1" t="n">
         <v>1</v>
       </c>
       <c r="DM135" t="n">
@@ -56307,7 +56313,7 @@
           <t>Fz</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C136" t="n">
